--- a/Coordenadoria/02_Dados_Tratados/base_diagonal_manutencao.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_diagonal_manutencao.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1246" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1390" uniqueCount="316">
   <si>
     <t>operador</t>
   </si>
@@ -118,6 +118,15 @@
     <t>2702</t>
   </si>
   <si>
+    <t>2722</t>
+  </si>
+  <si>
+    <t>2728</t>
+  </si>
+  <si>
+    <t>2709</t>
+  </si>
+  <si>
     <t>2703</t>
   </si>
   <si>
@@ -127,21 +136,12 @@
     <t>2719</t>
   </si>
   <si>
-    <t>2722</t>
+    <t>2742</t>
   </si>
   <si>
     <t>2729</t>
   </si>
   <si>
-    <t>2709</t>
-  </si>
-  <si>
-    <t>2728</t>
-  </si>
-  <si>
-    <t>2742</t>
-  </si>
-  <si>
     <t>ID5-15-03 ID5-15-06 ID5-15-08 ID5-15-20 TR DE MOTOR 2706 INSP 1 COR</t>
   </si>
   <si>
@@ -302,9 +302,6 @@
   </si>
   <si>
     <t>1. ID5-15-0A2. ID5-15-103. CORR42M4. 500H MOT5.MOT1M12 (MOT)6. MOT2M6 (MOT)7. 100H (BAT)8. ID5-15-079. GOVERNADOR (REVG)10. BEED VALVE (CRI)11. KIT HSI (HSI)12. CJ SOBRE SELV (MONT)13. RG / TROCA DE MOTOR 14. ID5-15-0216. ID5-15-0917. ID5-15-0118. ID5-15-1119. HSI20. BAT (12M)21. ID5-15-0622. ID-15-08</t>
-  </si>
-  <si>
-    <t>1. ID5-15-062. ID5-15-083. 3300H (MOT)4. MOT1M12 (MOT)5. MOT18A66. MOTA127. 100H (BAT)</t>
   </si>
   <si>
     <t>60M</t>
@@ -341,7 +338,7 @@
     <t>1. ID5-15-0A2. CORR12M3. 3300H (MOT)4. MOT1M12 (MOT)5. MOT2M6 (MOT)6. 100H (BAT)7. BAT ELT (TLV)</t>
   </si>
   <si>
-    <t>1. ID5-15-0A2. CORR60M3. 3400H (MOT)4. MOT1M12 (MOT)5. MOT2M6 (MOT)6. 100H (BAT)</t>
+    <t>1. ID5-15-062. ID5-15-083. 100H (MOT)4. MOT1M12 (MOT)7. 100H (BAT)8. CORR60M</t>
   </si>
   <si>
     <t>1. ID5-15-022. ID5-15-103. ID5-15-114. ID5-15-035.ID5-15-216.ID5-15-227.ID5-15-098.ID5-15-069.ID5-15-0110.ID5-15-0711.ID5-15-2012.5-15-1513.CORR30M14.CORR36M15. ENGINE MONT (IC)16. VACUM REGULAT; 1. ID5-15-022. ID5-15-103. ID5-15-114. ID5-15-035.ID5-15-216.ID5-15-227.ID5-15-098.ID5-15-069.ID5-15-0110.ID5-15-0711.ID5-15-2012.5-15-1513.CORR30M14.CORR36M15. ENGINE MONT (IC)16. VACUM REGULAT17. CORR42M</t>
@@ -356,19 +353,39 @@
     <t>1. ID5-15-0A3. CORR60M4. 300H (MOT)5. MOT1M12 (MOT)6. 100H (BAT)7. MOT2M6 (MOT)</t>
   </si>
   <si>
-    <t>ID5-15-0A,INSP1-27M,MOT 2900FH Data 16/03/26 início</t>
+    <t>1. ID5-15-062. ENGINE MONT (IC)3. 100H (MOT)4. MOT1M125. 100H (BAT)5. CJ SOBRE SELVA (MONT)</t>
+  </si>
+  <si>
+    <t>1. ID5-15-0A2. ID5-15-223. 200H (MOT)4. MOT1M12 (MOT)5. MOT2M6 (MOT)6. 100H (BAT)7. BAT ELT</t>
+  </si>
+  <si>
+    <t>ID5-15-0A
+INSP 1 (27M)
+MOT 2900FH
+INÍCIO: 16/03/26</t>
+  </si>
+  <si>
+    <t>ID5-15-0A
+INSP 1 (27M)
+MOT 2900FH</t>
   </si>
   <si>
     <t>1. ID5-15-062. ID5-15-0A3. ID5-15-074. ID5-15-205. ID5-15-016. ID5-15-047. ID5-15-098. CORR72M9. CORR66M10.ENGINE MOUNT(IC)11. ID5-15-2112. ID5-15-2213. ID5-15-0214. ID5-15-1115. ID5-15-0116. ID5-15-2017. ID5-15-0918. ID5-15-0319. CORR6M 20. ID5-15-1021. ID5-15-1222. ID5-15-0823. BAT ELT (TLV)24. CORR12M25. 3900H (MOT)26. MOT1M12 (MOT)27. MOT18A6 (MOT)28. MOTA1229. MOT2M6; 1. ID5-15-062. ID5-15-0A3. ID5-15-074. ID5-15-205. ID5-15-016. ID5-15-047. ID5-15-098. CORR72M9. CORR66M10.ENGINE MOUNT(IC)11. ID5-15-2112. ID5-15-2213. ID5-15-0214. ID5-15-1115. ID5-15-0116. ID5-15-2017. ID5-15-0918. ID5-15-0319. CORR6M 20. ID5-15-1021. ID5-15-1222. ID5-15-0823. BAT ELT (TLV)24.CORR12M; 1. ID5-15-202. ID5-15-223 .ENGINE MOUNT(IC)4. 3900H (MOT)5. MOT1M12 (MOT)6. MOT18A6 (MOT)7. MOTA128. MOT2M6; MONTAGEM DE MOTOR ( SERÁ INSTALADO O MOTOR QUE ESTÁ NA AERONAVE 2737</t>
   </si>
   <si>
+    <t>1. ID5-15-062. CORR42M3. 100H (MOT)4. MOT1M12 (MOT)5. 100H (BAT)6. AXLE MAIN GEAR</t>
+  </si>
+  <si>
+    <t>1. ID5-15-0A2. 200H (MOT)3. MOT1M12 (MOT)4. MOT2M6 (MOT)5. 100H (BAT)6. BAT ELT (IC) 7. STARTER GENERATOR (REVG)</t>
+  </si>
+  <si>
     <t>1. ID5-15-062. ID5-15-073. ID5-15-084. ID5-15-125. ID5-15-226. 3400H (MOT)7. MOT1M12 (MOT)8. 100H (BAT)9. GOVERNADOR DA HELICE (TBO)</t>
   </si>
   <si>
-    <t>1. ID5-15-062. ID5-15-073 ID5-15-224. 3500H (MOT)5. MOT1M12 (MOT)6. 100H (BAT)7. VALVE,COMPRESSOR (REVG)</t>
-  </si>
-  <si>
-    <t>ID5-15-0A,INSP1-27M,MOT 2900FH Data 02/04/26 fim</t>
+    <t>ID5-15-0A
+INSP 1 (27M)
+MOT 2900FH
+FIM: 02/04/26</t>
   </si>
   <si>
     <t>INSPEÇÃO
@@ -386,19 +403,22 @@
     <t>1. ID5-15-022. ID5-15-103. ID5-15-114. ID5-15-035.ID5-15-216.ID5-15-227.ID5-15-098.ID5-15-069.ID5-15-0110.ID5-15-0711.ID5-15-2012.5-15-1513.CORR30M14.CORR36M15. ENGINE MONT (IC)16. VACUM REGULAT17. CORR42M</t>
   </si>
   <si>
-    <t>1. ID5-15-202. ID5-15-223 .ENGINE MOUNT(IC)4. 3900H (MOT)5. MOT1M12 (MOT)6. MOT18A6 (MOT)7. MOTA128. MOT2M6; 1. ID5-15-222. MOTA123. 3900H; ANV SERÁ TRANFERIDA PARA BABE; MONTAGEM DE MOTOR ( SERÁ INSTALADO O MOTOR QUE ESTÁ NA AERONAVE 2737</t>
+    <t>1. CORR18M; 1. ID5-15-202. ID5-15-223 .ENGINE MOUNT(IC)4. 3900H (MOT)5. MOT1M12 (MOT)6. MOT18A6 (MOT)7. MOTA128. MOT2M6; ANV SERÁ TRANFERIDA PARA BABE; MONTAGEM DE MOTOR ( SERÁ INSTALADO O MOTOR QUE ESTÁ NA AERONAVE 2737</t>
   </si>
   <si>
     <t>1. ID5-15-062. CORR12M3.CORR18M4.CORR24M5.ID5-15-106.ID5-15-117.ID5-15-038.ID5-15-229.ID5-15-0210.ID5-15-0411.EXTINTOR 0112. ID5-15-2113. CORR30M14. CORR36M</t>
   </si>
   <si>
-    <t>1. ID5-15-062. CORR42M3. 100H (MOT)4. MOT1M12 (MOT)5. 100H (BAT)</t>
-  </si>
-  <si>
-    <t>1. ID5-15-062. ID5-15-223. ID5-15-114. 400H (MOT)5. MOT1M12 (MOT)7. 100H (BAT)8. 01 (EXTINGUISHER)</t>
-  </si>
-  <si>
-    <t>1. ID5-15-0A2 ID5-15-213. ID5-15-114. ID5-15-095. ID5-15-036. 3500H (MOT)7. MOT1M12 (MOT)8. MOT2M6 (MOT)6. 100H (BAT)</t>
+    <t>1. ID5-15-0A2. ID5-15-073. ID5-15-024. 200H (MOT)5. MOT1M12 (MOT)6. MOT2M6 (MOT)7. 100H (BAT)8. BAT ELT (IC)9. WHELL HALF (REVG)</t>
+  </si>
+  <si>
+    <t>1. ID5-15-062. ID5-15-223. ID5-15-114. 400H (MOT)5. MOT1M12 (MOT)7. 100H (BAT)</t>
+  </si>
+  <si>
+    <t>1. ID5-15-062. 300H (MOT)3. 100H (BAT)4. CORR48M5. MOT1M12 (MOT)</t>
+  </si>
+  <si>
+    <t>1. ID5-15-062. ID5-15-213 ID5-15-114 ID5-15-105 ID5-15-086 ID5-15-027 ID5-15-208. 300H (MOT)9. MOT1M12 (MOT)10. 100H (BAT)11 VALVE,COMPRESSOR (REVG) 12. CJ SOBRE SELV</t>
   </si>
   <si>
     <t>INSPEÇÃO
@@ -414,40 +434,51 @@
     <t>1. ID5-15-102. ID5-15-113. ID5-15-034.ID5-15-215.ID5-15-226.ID5-15-097.ID5-15-068.ID5-15-079.ID5-15-2010.5-15-1511. ENGINE MONT (IC)12. VACUM REGULAT</t>
   </si>
   <si>
-    <t>1. CORR18M; 1. LIFE RAFT (REVG)2. MOT2M6; ANV SERÁ TRANFERIDA PARA BABE</t>
+    <t>1. ID5-15-072. ID5-15-093. ID5-15-0A4. ID5-15-015. CORR24M6. ID5-15-067. ID5-15-20; 1. LIFE RAFT (REVG); ANV SERÁ TRANFERIDA PARA BABE</t>
   </si>
   <si>
     <t>1. ID5-15-102.ID5-15-223.ID5-15-214.ID5-15-045.ID5-15-0306.ID5-15-04</t>
   </si>
   <si>
-    <t>1. ID5-15-072. CORR18M3. ID5-15-064. ID5-15-205. ID5-15-01; HSI</t>
-  </si>
-  <si>
-    <t>1. ID5-15-0A2. ID5-15-083. 3600H (MOT)4. MOT1M12 (MOT)5. MOT2M66. 100H (BAT)</t>
-  </si>
-  <si>
-    <t>ID5-15-06, ID5-15-08, ID5-15-09,INSP2-30M,MOT-3000FH PREVSÃO 22/06/26</t>
-  </si>
-  <si>
-    <t>1. 01 (EXTINGUISHER)2.  ID5-15-083. VACUM REGULAT</t>
-  </si>
-  <si>
-    <t>1. ID5-15-072. ID5-15-083. ID5-15-0A4. ID5-15-01; ANV SERÁ TRANFERIDA PARA BABE</t>
-  </si>
-  <si>
-    <t>1. RG</t>
-  </si>
-  <si>
-    <t>1. ID5-15-0A2. ID5-15-083. ID5-15-094. ID5-15-025. ID5-15-216. 500H (MOT)7. MOT1M12 (MOT)8. 100H (BAT)</t>
-  </si>
-  <si>
-    <t>1. ID5-15-062. ID5-15-213. ID5-15-204. ID5-15-115. ID5-15-086. ID5-15-027. 3. ID5-15-108. 3700H (MOT)9. MOT1M12 (MOT)10. MOT2M6 (MOT)11. 100H (BAT)</t>
+    <t>1. ID5-15-0A2. ID5-15-083. WHELL HALF (REVG)4. 400H (MOT)5. 100H (BAT)6. EXTINTOR (01)7. CONJ SELVA (MONT)8. BAT ELT (IC)9. MOT1M12 (MOT)10. MOT2M6 (MOT)</t>
+  </si>
+  <si>
+    <t>1. ID5-15-0A2 ID5-15-213. ID5-15-114. ID5-15-095. ID5-15-036. 3500H (MOT)7. MOT1M12 (MOT)8. MOT2M6 (MOT)6. 100H (BAT); HSI</t>
+  </si>
+  <si>
+    <t>RG</t>
+  </si>
+  <si>
+    <t>ID5-15-06
+ID5-15-08
+ID5-15-09
+INSP 2 (30M)
+MOT 3000FH
+INÍCIO: 15/06/26</t>
+  </si>
+  <si>
+    <t>ID5-15-06
+ID5-15-08
+ID5-15-09
+INSP 2 (30M)
+MOT 3000FH</t>
   </si>
   <si>
     <t>INSPEÇÃO
 0A/07
-7900HS
-INSP MOT
+7900HS</t>
+  </si>
+  <si>
+    <t>ANV SERÁ TRANFERIDA PARA BABE</t>
+  </si>
+  <si>
+    <t>1. ID5-15-0A2. ID5-15-083. ID5-15-094. ID5-15-025. ID5-15-216. 500H (MOT)7. MOT1M12 (MOT)8. 100H (BAT)9. MOT2M6</t>
+  </si>
+  <si>
+    <t>1. EXTINGUISHER; 1. LIFE RAFT (REVG); RG</t>
+  </si>
+  <si>
+    <t>INSP MOT
 4400FH</t>
   </si>
   <si>
@@ -457,16 +488,30 @@
     <t>MOT1M12 Motor_DATA</t>
   </si>
   <si>
-    <t>1. ID5-15-012. ID5-15-093. ID5-15-204. ID5-15-075. ID5-15-0A</t>
+    <t>1. 01 (EXTINGUISHER)2.  ID5-15-083. VACUM REGULAT</t>
+  </si>
+  <si>
+    <t>1. ID5-15-012. ID5-15-093. ID5-15-074. ID5-15-0A</t>
   </si>
   <si>
     <t>1. ID5-15-062. ID5-15-073. 600H (MOT)4. MOT1M12 (MOT)5. MOT2M6 (MOT)6. BATERIA ELT (CRI 12M)7. 100H (BAT)</t>
   </si>
   <si>
-    <t>1. 5-15-MB-B2. CORR12M3. ID5-15-0A</t>
-  </si>
-  <si>
-    <t>1. ID5-15-0A2. ID5-15-093. ID5-15-074. CORR66M5. ID5-15-016. 3800H (MOT)7. MOT1M12 (MOT)8. MOT2M6 (MOT)9. 100H (BAT)10. LIFE RAFT11. 01 EXTINTOR</t>
+    <t>1. ID5-15-062. 500H(MOT)3. MOT1M12 (MOT)4. 100H (BAT)5. ID5-15-207. ID5-15-22</t>
+  </si>
+  <si>
+    <t>1. ID5-15-072. CORR18M3. ID5-15-064. ID5-15-205. ID5-15-01</t>
+  </si>
+  <si>
+    <t>100H_MOTOR ID5-15-06B (AT_609%794)</t>
+  </si>
+  <si>
+    <t>ID5-15-06
+ID5-15-08
+ID5-15-09
+INSP 2 (30M)
+MOT 3000FH
+FIM: XX/08/26</t>
   </si>
   <si>
     <t>INSPEÇÃO
@@ -477,13 +522,10 @@
 4500FH</t>
   </si>
   <si>
-    <t>100H_MOTOR ID5-15-06B (AT_609%794)</t>
-  </si>
-  <si>
     <t>1. ID5-15-0A</t>
   </si>
   <si>
-    <t>1. ID5-15-0A2. 5-15-MG-B3. CORR66M4. 700H (MOT)5. MOT1M12 (MOT)3. 100H (BAT)</t>
+    <t>1. ID5-15-062. ID5-15-083. 300H (MOT)4. MOT1M12 (MOT)5. 100H (BAT)</t>
   </si>
   <si>
     <t>ID4-15-07 ANV DATA</t>
@@ -496,13 +538,13 @@
 4600FH</t>
   </si>
   <si>
-    <t>1. ID5-15-10</t>
-  </si>
-  <si>
-    <t>1. ID5-15-072. ID5-15-0A3. BAT ELT (IC 12M)4. MOT2M65. MOT1M12</t>
-  </si>
-  <si>
-    <t>ID5-15-0A,ID5-15-01,ID5-15-07,INSP1-33M,MOT 3100FH</t>
+    <t>1. ID5-15-0A; 1. ID5-15-202. ID5-15-013. ID5-15-094. CORR48M5. RG (MOT)6. 5-15-MB-B7. VALVE ASSEMBLE (IC)8. EXTINGUISHER (01)9. LIFE RAFT(RG); HSI</t>
+  </si>
+  <si>
+    <t>1. ID5-15-0A2. 5-15-MG-B3. CORR66M4. 700H (MOT)5. MOT1M12 (MOT)3. 100H (BAT)</t>
+  </si>
+  <si>
+    <t>1. ID5-15-0A2. 600H(MOT)3. MOT1M12 (MOT)4. MOT2M6 (MOT)5. 100H (BAT)6. ID5-15-097. ID5-15-018. CORR54M9. ID5-15-0710. AXLE MAIN GEAR 11. VACUUM REGULAT (TROCA FILT)12. BAT ELT (IC)13. BAT (12M)</t>
   </si>
   <si>
     <t>INSPEÇÃO
@@ -515,10 +557,18 @@
     <t>ID5-15-10</t>
   </si>
   <si>
-    <t>1. ID5-15-202. ID5-15-013. ID5-15-094. CORR48M5. ID5-15-066. BAT (12M)7. EXTINTOR (IC)8. REVG WHEEL HALF9. REVG WHEEL HALF</t>
-  </si>
-  <si>
     <t>1. ID5-15-062. 800H (MOT)3. MOT1M12 (MOT)4. MOT2M6 (MOT)5. 100H (BAT)</t>
+  </si>
+  <si>
+    <t>ID5-15-0A
+ID5-15-01
+ID 5-15-06
+ID5-15-07
+ID 5-15-20
+ID5-15-MG
+INSP 1 (33M)
+MOT 3100FH
+MOT1M12</t>
   </si>
   <si>
     <t>INSPEÇÃO
@@ -537,13 +587,7 @@
     <t>ID5-15-07/08</t>
   </si>
   <si>
-    <t>1. ID5-15-082. ID5-15-063. CORR48M4. 5-15-MB-B</t>
-  </si>
-  <si>
-    <t>1. CORR36M</t>
-  </si>
-  <si>
-    <t>3200fh mot</t>
+    <t>1. CORR48M</t>
   </si>
   <si>
     <t>INSPEÇÃO
@@ -569,31 +613,19 @@
 ID 5-15-22</t>
   </si>
   <si>
-    <t>RECEBIDO  DO    PAMA-LS</t>
-  </si>
-  <si>
-    <t>RECEBIDO  DA  EEAR</t>
-  </si>
-  <si>
-    <t>01,02,09,11          COR 12 M        LPS3       MOLAS</t>
-  </si>
-  <si>
-    <t>RECEBIMENTO PAMA-LS</t>
-  </si>
-  <si>
-    <t>0A,15       20,MG         4300 FH          COR 54 M</t>
-  </si>
-  <si>
-    <t>06,02,10        11,21,22       200 FH</t>
-  </si>
-  <si>
-    <t>01,06,08       09,20       4400 FH      TBO MOTOR</t>
-  </si>
-  <si>
-    <t>CT DISK, FCU, HELICE, BOMBA COMB</t>
-  </si>
-  <si>
-    <t>LIMALHA MOTOR  -  (TROCA MOTOR)</t>
+    <t>1. CORR42M</t>
+  </si>
+  <si>
+    <t>ID 20 VENC 13/11/26======0A,20 700 FH</t>
+  </si>
+  <si>
+    <t>ANV SERÁ ENTREGUE BABRINSP COR 07/04AT %1994 (EXT 30 D)======ID 0A 300 FH COR 18 M</t>
+  </si>
+  <si>
+    <t>INSP COR 25/03AT %1995 (EXT 15 D) - 09/04/26AT %2013 (MAIS 15 D) - 24/04/24AT%2014 (EXT 10 H ID 0A, 5 H ID 10)AT%2012 (EXT 10 H MOT)ID 01,09,20 - 24/04TBO MOT DISP 120:35======0A,01 09,10,20 3900 FH COR 54 M</t>
+  </si>
+  <si>
+    <t>01,06,07 08,09,10</t>
   </si>
   <si>
     <t>ID 5-15-0A
@@ -610,54 +642,26 @@
 2600 FH</t>
   </si>
   <si>
-    <t>ID 01,06,08        09,20       4400 FH      TBO MOTOR</t>
-  </si>
-  <si>
-    <t>ID 20</t>
-  </si>
-  <si>
-    <t>COR 42 M</t>
-  </si>
-  <si>
-    <t>ID 5-15-0A
-ID 5-15-06
-ID 5-15-07
-ID 5-15-08
-3000 FH</t>
-  </si>
-  <si>
-    <t>ID5-15-06B (5500FH) E 200FH MOTORES DE 15 A 19 DEZ</t>
-  </si>
-  <si>
-    <t>ID 5-15-07</t>
+    <t>RECEBIDO DA EPCAR EM 11/06/26</t>
+  </si>
+  <si>
+    <t>RECEBIDO DA EEAR EM 09/04/26</t>
+  </si>
+  <si>
+    <t>RECEBIMENTO BASM EM 21/01/26</t>
+  </si>
+  <si>
+    <t>0A,15 20,MG 4300 FH COR 54 M</t>
+  </si>
+  <si>
+    <t>0A,01 09,10,20 3900 FH COR 54 M</t>
+  </si>
+  <si>
+    <t>CT DISK, FCU, HELICE, BOMBA COMB</t>
   </si>
   <si>
     <t>ID 5-15-0A
 500 FH</t>
-  </si>
-  <si>
-    <t>1. EXTINTOR (01)</t>
-  </si>
-  <si>
-    <t>ID 06         800 FH</t>
-  </si>
-  <si>
-    <t>06,10,12       4400 FH</t>
-  </si>
-  <si>
-    <t>01,06,09           2600 FH      COR 24 M</t>
-  </si>
-  <si>
-    <t>ID 0A    4700 FH      TBO MOTOR</t>
-  </si>
-  <si>
-    <t>HSI, CT DISK, FCU, GOV SOBRE, GERADOR, TREM AUX. VHF, MANG, BUCHA TPA, ARAME DETEC FOGO MOT, MOTOR ELETR FLAP</t>
-  </si>
-  <si>
-    <t>HSI TRAVADO</t>
-  </si>
-  <si>
-    <t>ID5-15-06B (5900FH) E 800FH MOTORES 10 a 18 SET NO PAMALS??</t>
   </si>
   <si>
     <t>ID 5-15-0A
@@ -665,7 +669,35 @@
 3500 FH</t>
   </si>
   <si>
-    <t>ID 5-15-20 [1]</t>
+    <t>ID5-15-06B (5500FH) E 200FH MOTORES DE 15 A 19 DEZ</t>
+  </si>
+  <si>
+    <t>ID 5-15-07</t>
+  </si>
+  <si>
+    <t>ID 5-15-0A
+ID 5-15-10
+ID 5-15-12
+ID 5-15-20
+3100 FH</t>
+  </si>
+  <si>
+    <t>1. EXTINTOR (01)</t>
+  </si>
+  <si>
+    <t>EEAR</t>
+  </si>
+  <si>
+    <t>01,02,09,11 COR 12 M LPS3 MOLAS</t>
+  </si>
+  <si>
+    <t>HSI, CT DISK, FCU, GOV SOBRE, GERADOR, TREM AUX. VHF, MANG, BUCHA TPA, ARAME DETEC FOGO MOT, MOTOR ELETR FLAP</t>
+  </si>
+  <si>
+    <t>ANV ACIDENTADA</t>
+  </si>
+  <si>
+    <t>ID5-15-06B (5900FH) E 800FH MOTORES 10 a 18 SET NO PAMALS??</t>
   </si>
   <si>
     <t>ID 5-15-04
@@ -675,46 +707,16 @@
 2300 FH</t>
   </si>
   <si>
-    <t>ID 5-15-10 [1]</t>
-  </si>
-  <si>
     <t>ID 5-15-0A
 ID 5-15-06
 ID 5-15-10
 3100 FH</t>
   </si>
   <si>
-    <t>EEAR</t>
-  </si>
-  <si>
-    <t>EEXD</t>
-  </si>
-  <si>
-    <t>ID 07</t>
-  </si>
-  <si>
-    <t>ANV ENTREGUE A BABR  -  ETA 6</t>
-  </si>
-  <si>
-    <t>0A,01       09,10,20        3900 FH            COR 54 M</t>
-  </si>
-  <si>
-    <t>0A,07           100 FH      COR 66 M</t>
-  </si>
-  <si>
-    <t>01,06,07         08,09,10</t>
-  </si>
-  <si>
-    <t>SIST HSI</t>
-  </si>
-  <si>
-    <t>GIRO / HSI</t>
-  </si>
-  <si>
-    <t>ID 06            2800 FH</t>
-  </si>
-  <si>
-    <t>ID 06,07           3200 FH</t>
+    <t>1. 5-15-MB-B</t>
+  </si>
+  <si>
+    <t>ID 07 - VENC 21/03AT 377%0274 (EXT 20 D)======ID 07</t>
   </si>
   <si>
     <t>ID5-15-0A, 01 e 20 (5600FH) E 300FH MOTORES DE 03 A 12 FEV NA BACO</t>
@@ -728,30 +730,23 @@
 600 FH</t>
   </si>
   <si>
-    <t>1. ID5-15-062. ID5-15-123.CORR42M</t>
-  </si>
-  <si>
-    <t>ID 06        4000 FH</t>
-  </si>
-  <si>
-    <t>T5 ALTA</t>
-  </si>
-  <si>
-    <t>06,07,08         10,20,22         100 FH</t>
-  </si>
-  <si>
-    <t>ID 0A            300 FH           COR 18 M</t>
-  </si>
-  <si>
-    <t>0A,02       07,10,11      21,22     2900 FH</t>
-  </si>
-  <si>
-    <t>HSI</t>
-  </si>
-  <si>
     <t>ID 5-15-0A
-ID 5-15-12
-3100 FH</t>
+ID 5-15-06
+3200 FH</t>
+  </si>
+  <si>
+    <t>1. ID5-15-062. ID5-15-123. ID5-15-204. CORR48M</t>
+  </si>
+  <si>
+    <t>06,02,10 11,21,22 200 FH</t>
+  </si>
+  <si>
+    <t>LIMALHA MOTOR - (TROCA MOTOR)</t>
+  </si>
+  <si>
+    <t>ID 5-15-0A
+ID 5-15-07
+3600 FH</t>
   </si>
   <si>
     <t>ID 5-15-0A
@@ -774,51 +769,19 @@
 2700 FH</t>
   </si>
   <si>
-    <t>ID 5-15-0A
-ID 5-15-07
-3600 FH</t>
-  </si>
-  <si>
-    <t>1. ID5-15-0A2. ID5-15-013. CORR54M4. ID5-15-205. ID5-15-096. ID5-15-07</t>
-  </si>
-  <si>
-    <t>0A,20        21,22        4100 FH</t>
-  </si>
-  <si>
-    <t>0A,20        4500 FH      TBO MOTOR</t>
-  </si>
-  <si>
-    <t>CB IND FLAP</t>
-  </si>
-  <si>
-    <t>0A,10,22          2700 FH</t>
-  </si>
-  <si>
-    <t>ID 06,07           2200 FH</t>
-  </si>
-  <si>
-    <t>ID 0A           200 FH</t>
-  </si>
-  <si>
-    <t>STALL / FLAP</t>
-  </si>
-  <si>
-    <t>06,08         4000 FH</t>
-  </si>
-  <si>
-    <t>ID 0A        100 FH         COR 42 M</t>
-  </si>
-  <si>
-    <t>RECOLHIDA</t>
-  </si>
-  <si>
-    <t>01,09,20        HSI             COR 48 M</t>
-  </si>
-  <si>
-    <t>0A,02      07,10,11      21,22     2900 FH</t>
-  </si>
-  <si>
-    <t>ANV ACIDENTADA</t>
+    <t>1. ID5-15-012. CORR54M3. ID5-15-064. ID5-15-205. ID5-15-096. ID5-15-07</t>
+  </si>
+  <si>
+    <t>ID 0A 500 FH</t>
+  </si>
+  <si>
+    <t>T5 ALTA</t>
+  </si>
+  <si>
+    <t>0.15</t>
+  </si>
+  <si>
+    <t>ID 02,11,21,22 VENC 09/07ID 10 VENC 10/07ID 07 VENC 19/08======0A,02 07,10,11 21,22 2900 FH</t>
   </si>
   <si>
     <t>ID 5-15-01
@@ -831,37 +794,57 @@
   </si>
   <si>
     <t>ID 5-15-0A
+3300 FH</t>
+  </si>
+  <si>
+    <t>ID 5-15-0A
 ID 5-15-06
 2500 FH</t>
   </si>
   <si>
-    <t>ID 0A           500 FH</t>
-  </si>
-  <si>
-    <t>ID 0A,08          2300 FH</t>
-  </si>
-  <si>
-    <t>06,09,21           300 FH</t>
-  </si>
-  <si>
-    <t>0A,07,09            15,20,MG         4300 FH          COR 54 M</t>
-  </si>
-  <si>
-    <t>0A,07,09           15,20,MG         4300 FH          COR 54 M</t>
-  </si>
-  <si>
-    <t>06,21,22        200 FH</t>
-  </si>
-  <si>
-    <t>0A,07        4100 FH</t>
-  </si>
-  <si>
-    <t>ID 5-15-01
+    <t>AT %2097 (EXT 10 H ID 06)AT %2108 (EXT 10 H MOT)ID 07 - 25/06/26======ID 06,07           2200 FH</t>
+  </si>
+  <si>
+    <t>ID 01,09,20 VENC 19/08COR 48 M VENC 03/09======01,09,20 HSI COR 48 M</t>
+  </si>
+  <si>
+    <t>ID 5-15-0A
+ID 5-15-14
+ID 5-15-15
+700 FH</t>
+  </si>
+  <si>
+    <t>ID 5-15-0A
+ID 5-15-01
+ID 5-15-06
 ID 5-15-09
 ID 5-15-11
 ID 5-15-20
 ID 5-15-21
-ID 5-15-22</t>
+ID 5-15-22
+3700 FH</t>
+  </si>
+  <si>
+    <t>ID 5-15-0A
+2800 FH</t>
+  </si>
+  <si>
+    <t>ID 5-15-03</t>
+  </si>
+  <si>
+    <t>ID 02,11 VENC 13/11/26COR 60 M VENCE 08/12======</t>
+  </si>
+  <si>
+    <t>AT %2088 (EXT 9:40 ID 06)======06,08 4000 FH</t>
+  </si>
+  <si>
+    <t>RECOLHIDA</t>
+  </si>
+  <si>
+    <t>0A,02 07,10,11 21,22 2900 FH</t>
+  </si>
+  <si>
+    <t>HSI TRAVADO</t>
   </si>
   <si>
     <t>ID 5-15-01
@@ -869,34 +852,6 @@
 ID 5-15-20</t>
   </si>
   <si>
-    <t>ID 5-15-03</t>
-  </si>
-  <si>
-    <t>ID 04,06           600 FH</t>
-  </si>
-  <si>
-    <t>06,08,MG        4200 FH</t>
-  </si>
-  <si>
-    <t>06,20,21          2800 FH</t>
-  </si>
-  <si>
-    <t>06,08       4400 FH</t>
-  </si>
-  <si>
-    <t>03,06       07,08,20           400 FH</t>
-  </si>
-  <si>
-    <t>ID 06           200 FH</t>
-  </si>
-  <si>
-    <t>0A,01         09,20        3300 FH</t>
-  </si>
-  <si>
-    <t>ID 5-15-0A
-2800 FH</t>
-  </si>
-  <si>
     <t>ID5-15-0A (6000FH) E 900FH MOTORES DE 9 A 13 NOV NA BACO</t>
   </si>
   <si>
@@ -904,48 +859,34 @@
 300 FH</t>
   </si>
   <si>
-    <t>06,08        100 FH</t>
-  </si>
-  <si>
-    <t>ID 06,20        2400 FH      COR 18 M</t>
-  </si>
-  <si>
-    <t>0A,01        02,11          400 FH          COR 72 M</t>
-  </si>
-  <si>
-    <t>ID 06           4200 FH</t>
-  </si>
-  <si>
-    <t>ID5-15-06B, 09, 11 (5700FH) E INSTALAÇÃO DO MOTOR PCE-PC0743.</t>
+    <t>ID 01,09 VENC 17/11COR 12 M VENC 07/10======0A,01 07,09 4300 FH COR 12 M</t>
+  </si>
+  <si>
+    <t>ID 06 4000 FH</t>
+  </si>
+  <si>
+    <t>STALL / FLAP</t>
+  </si>
+  <si>
+    <t>COR 42 M 20/05AT %2066 (EXT 30 D)PEDIR EXT MOT======ID 0A 100 FH COR 42 M</t>
+  </si>
+  <si>
+    <t>ID 20</t>
+  </si>
+  <si>
+    <t>01,09,20 HSI COR 48 M</t>
+  </si>
+  <si>
+    <t>INSP COR (17/02/26)AT %1927 (EXT ATÉ 26/02)======COR 42 M</t>
   </si>
   <si>
     <t>ID 5-15-0A
 ID 5-15-06
+ID 5-15-12
 3300 FH</t>
   </si>
   <si>
-    <t>0A,01             07,09             4300 FH        COR 6 M</t>
-  </si>
-  <si>
-    <t>ID 0A          2900 FH</t>
-  </si>
-  <si>
-    <t>ID 0A,01        4500 FH</t>
-  </si>
-  <si>
-    <t>0A,01,09       500 FH      COR 24 M</t>
-  </si>
-  <si>
-    <t>0A,02       03,11        300 FH</t>
-  </si>
-  <si>
-    <t>ID 0A         300 FH</t>
-  </si>
-  <si>
-    <t>ID 06           3000 FH</t>
-  </si>
-  <si>
-    <t>ID 06           3400 FH</t>
+    <t>ID5-15-06B, 09, 11 (5700FH) E INSTALAÇÃO DO MOTOR PCE-PC0743.</t>
   </si>
   <si>
     <t>ID 5-15-0A
@@ -953,16 +894,19 @@
 2900 FH</t>
   </si>
   <si>
-    <t>0A,ME,MG           700 FH      COR 60 M</t>
-  </si>
-  <si>
-    <t>ID 0A,07        200 FH</t>
-  </si>
-  <si>
-    <t>ID 06          500 FH</t>
-  </si>
-  <si>
-    <t>ID 0A,MG      4300 FH       COR 60 M</t>
+    <t>0A,01 07,09 4300 FH COR 12 M</t>
+  </si>
+  <si>
+    <t>CB IND FLAP</t>
+  </si>
+  <si>
+    <t>PAMA-LS EM 10/06/26</t>
+  </si>
+  <si>
+    <t>ID 07,09 VENC 30/07======0A,07,09 15,20,MG 4300 FH COR 54 M</t>
+  </si>
+  <si>
+    <t>ID 03 02/08ID 07,20 07/10======03,06 07,08,20 400 FH</t>
   </si>
   <si>
     <t>ID 5-15-0A
@@ -972,40 +916,193 @@
 400 FH</t>
   </si>
   <si>
-    <t>TBO        4500 FH</t>
-  </si>
-  <si>
-    <t>ID 0A,12           2500 FH</t>
-  </si>
-  <si>
-    <t>ID 06       4600 FH       COR 60 M</t>
-  </si>
-  <si>
-    <t>TBO          MOTOR        4700 H</t>
-  </si>
-  <si>
-    <t>TBO          MOTOR</t>
-  </si>
-  <si>
-    <t>ID 06         400 FH       COR 48 M</t>
-  </si>
-  <si>
-    <t>0A,08      3100 FH       COR 54 M</t>
-  </si>
-  <si>
-    <t>0A,08      3500 FH</t>
-  </si>
-  <si>
-    <t>DISP TBO</t>
-  </si>
-  <si>
-    <t>TBO           4000 H</t>
-  </si>
-  <si>
     <t>ID 5-15-0A
 ID 5-15-08
-ID 5-15-12
 3400 FH</t>
+  </si>
+  <si>
+    <t>ID 5-15-0A
+ID 5-15-06
+ID 5-15-07
+ID 5-15-08
+3000 FH</t>
+  </si>
+  <si>
+    <t>06 1200 FH</t>
+  </si>
+  <si>
+    <t>0A 1100 FH</t>
+  </si>
+  <si>
+    <t>AT%2227 EXT 10 H CELID 04 VENC 27/08======ID 04,06</t>
+  </si>
+  <si>
+    <t>ID 06 1000 FH COR 66 M</t>
+  </si>
+  <si>
+    <t>ID 0A 1300 FH</t>
+  </si>
+  <si>
+    <t>ID 0A 900 FH</t>
+  </si>
+  <si>
+    <t>06,08 100 FH</t>
+  </si>
+  <si>
+    <t>EEXD</t>
+  </si>
+  <si>
+    <t>ID 0A,07 200 FH</t>
+  </si>
+  <si>
+    <t>ID 12 VENC 30/03ID 10 VENC 14/05======06,10,12 4400 FH COR 18 M</t>
+  </si>
+  <si>
+    <t>ID 20 - 29/07ID 21,22 - 02/08======0A,20 21,22 4100 FH</t>
+  </si>
+  <si>
+    <t>ID 20 VENC 20/7======</t>
+  </si>
+  <si>
+    <t>TBO 4500 FH</t>
+  </si>
+  <si>
+    <t>01,06,09 2600 FH COR 24 M</t>
+  </si>
+  <si>
+    <t>AT%2232 (EXT 10 H)======ID 0A,08 2300 FH</t>
+  </si>
+  <si>
+    <t>ID 01,09 - 25/03/27COR 24 M - 30/03/27======01,06,09 2600 FH COR 24 M</t>
+  </si>
+  <si>
+    <t>ID 06 3000 FH HSI</t>
+  </si>
+  <si>
+    <t>ID 0A 2900 FH COR 30 M</t>
+  </si>
+  <si>
+    <t>ID 0A,12 2500 FH</t>
+  </si>
+  <si>
+    <t>ID 20 19/11/26COR 18 M 25/09/26======ID 06,20 2400 FH COR 18 M</t>
+  </si>
+  <si>
+    <t>ID 20 VENC 01/10ID 21 VENC 11/08======06,20,21 2800 FH</t>
+  </si>
+  <si>
+    <t>ID 22 VENC 25/06======0A,10,22 2700 FH</t>
+  </si>
+  <si>
+    <t>02,06,11 300 FH COR 72 M</t>
+  </si>
+  <si>
+    <t>AT %2243 EXT 10 H CELAT %2244 EXT 10 H MOT======06,08 4400 FH</t>
+  </si>
+  <si>
+    <t>COR 60 M VENC 08/01/27======ID 06 4600 FH COR 60 M</t>
+  </si>
+  <si>
+    <t>ID 01 VENC 13/09======0A,01 200 FH</t>
+  </si>
+  <si>
+    <t>ID 01 VENC 21/10======ID 0A,01 4500 FH</t>
+  </si>
+  <si>
+    <t>ID 02,11 VENC 21/10======02,06,11 300 FH COR 72 M</t>
+  </si>
+  <si>
+    <t>ID 06 4600 FH COR 60 M</t>
+  </si>
+  <si>
+    <t>ID 09 VENC 25/07ID 21 VENC 30/07======06,07 08,09,21 100 FH COR 66 M</t>
+  </si>
+  <si>
+    <t>ID 10,22 VENC 20/05ID 20 VENCE 30/05======</t>
+  </si>
+  <si>
+    <t>TBO MOTOR 4700 H</t>
+  </si>
+  <si>
+    <t>0A,01,09 500 FH COR 24 M</t>
+  </si>
+  <si>
+    <t>ANV ENTREGUE A BABR - ETA 6 EM 15/04/26</t>
+  </si>
+  <si>
+    <t>ID 01,09 07/10COR 24 M OUT======0A,01,09 500 FH COR 24 M</t>
+  </si>
+  <si>
+    <t>ID 03 02/08ID 01,07,09,20 07/10======03,06 07,08,20 400 FH</t>
+  </si>
+  <si>
+    <t>02,03,06 11,21,22 400 FH COR 72 M</t>
+  </si>
+  <si>
+    <t>0A,07 100 FH COR 66 M</t>
+  </si>
+  <si>
+    <t>0A,07 4100 FH</t>
+  </si>
+  <si>
+    <t>AT %2245 EXT 10 H CELAT %2246 EXT 10 H MOT======ID 06 4200 FH</t>
+  </si>
+  <si>
+    <t>COR 60 M VENC 29/10======</t>
+  </si>
+  <si>
+    <t>ID 02,11,21,22 VENC 25/09ID 03 VENC 09/11======02,03,06 11,21,22 400 FH COR 72 M</t>
+  </si>
+  <si>
+    <t>ID 06 200 FH</t>
+  </si>
+  <si>
+    <t>ID 0A 300 FH</t>
+  </si>
+  <si>
+    <t>ID 0A,MG 4300 FH COR 60 M</t>
+  </si>
+  <si>
+    <t>TBO MOTOR</t>
+  </si>
+  <si>
+    <t>CALENDÁRICAS VENC 17/03AT %1966 (EXT ATÉ 30/03)======01,06,07 08,09,10</t>
+  </si>
+  <si>
+    <t>COR 48 M - DEZ======ID 06 400 FH COR 48 M</t>
+  </si>
+  <si>
+    <t>SIST HSI</t>
+  </si>
+  <si>
+    <t>0A,08 3100 FH COR 54 M</t>
+  </si>
+  <si>
+    <t>AT %2001 (EXT 10 H)======ID 06 2800 FH</t>
+  </si>
+  <si>
+    <t>GIRO / HSI</t>
+  </si>
+  <si>
+    <t>HSI</t>
+  </si>
+  <si>
+    <t>ID 06 3000 FH</t>
+  </si>
+  <si>
+    <t>ID 06 3200 FH</t>
+  </si>
+  <si>
+    <t>ID 06 3400 FH COR 60 M</t>
+  </si>
+  <si>
+    <t>ID 07 VENC 20/06ID 01,09,20 VENC 30/08======0A,07,01 09,20 3300 FH</t>
+  </si>
+  <si>
+    <t>ID 0A 3500 FH</t>
+  </si>
+  <si>
+    <t>TBO 4000 H</t>
   </si>
   <si>
     <t>ID5-15-0A, 07, 08 (5800FH) E 700FH MOTORES 20 A 24 NA BACO</t>
@@ -1379,7 +1476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F311"/>
+  <dimension ref="A1:F347"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1419,7 +1516,7 @@
         <v>42</v>
       </c>
       <c r="F2" t="s">
-        <v>294</v>
+        <v>313</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1439,7 +1536,7 @@
         <v>43</v>
       </c>
       <c r="F3" t="s">
-        <v>294</v>
+        <v>313</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1459,7 +1556,7 @@
         <v>44</v>
       </c>
       <c r="F4" t="s">
-        <v>294</v>
+        <v>313</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1479,7 +1576,7 @@
         <v>45</v>
       </c>
       <c r="F5" t="s">
-        <v>294</v>
+        <v>313</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1499,7 +1596,7 @@
         <v>46</v>
       </c>
       <c r="F6" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1519,7 +1616,7 @@
         <v>47</v>
       </c>
       <c r="F7" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1539,7 +1636,7 @@
         <v>48</v>
       </c>
       <c r="F8" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1559,7 +1656,7 @@
         <v>48</v>
       </c>
       <c r="F9" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1579,7 +1676,7 @@
         <v>48</v>
       </c>
       <c r="F10" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1599,7 +1696,7 @@
         <v>49</v>
       </c>
       <c r="F11" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1619,7 +1716,7 @@
         <v>50</v>
       </c>
       <c r="F12" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1639,7 +1736,7 @@
         <v>51</v>
       </c>
       <c r="F13" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1659,7 +1756,7 @@
         <v>51</v>
       </c>
       <c r="F14" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1679,7 +1776,7 @@
         <v>51</v>
       </c>
       <c r="F15" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1699,7 +1796,7 @@
         <v>52</v>
       </c>
       <c r="F16" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1719,7 +1816,7 @@
         <v>53</v>
       </c>
       <c r="F17" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -1739,7 +1836,7 @@
         <v>49</v>
       </c>
       <c r="F18" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1759,7 +1856,7 @@
         <v>54</v>
       </c>
       <c r="F19" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1779,7 +1876,7 @@
         <v>55</v>
       </c>
       <c r="F20" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1799,7 +1896,7 @@
         <v>55</v>
       </c>
       <c r="F21" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -1819,7 +1916,7 @@
         <v>55</v>
       </c>
       <c r="F22" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -1839,7 +1936,7 @@
         <v>56</v>
       </c>
       <c r="F23" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -1859,7 +1956,7 @@
         <v>53</v>
       </c>
       <c r="F24" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -1879,7 +1976,7 @@
         <v>54</v>
       </c>
       <c r="F25" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -1899,7 +1996,7 @@
         <v>57</v>
       </c>
       <c r="F26" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -1919,7 +2016,7 @@
         <v>58</v>
       </c>
       <c r="F27" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -1939,7 +2036,7 @@
         <v>58</v>
       </c>
       <c r="F28" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -1959,7 +2056,7 @@
         <v>58</v>
       </c>
       <c r="F29" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -1979,7 +2076,7 @@
         <v>56</v>
       </c>
       <c r="F30" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -1999,7 +2096,7 @@
         <v>59</v>
       </c>
       <c r="F31" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -2019,7 +2116,7 @@
         <v>60</v>
       </c>
       <c r="F32" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -2039,7 +2136,7 @@
         <v>61</v>
       </c>
       <c r="F33" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -2059,7 +2156,7 @@
         <v>62</v>
       </c>
       <c r="F34" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -2079,7 +2176,7 @@
         <v>62</v>
       </c>
       <c r="F35" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -2099,7 +2196,7 @@
         <v>62</v>
       </c>
       <c r="F36" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -2119,7 +2216,7 @@
         <v>63</v>
       </c>
       <c r="F37" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -2139,7 +2236,7 @@
         <v>64</v>
       </c>
       <c r="F38" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -2159,7 +2256,7 @@
         <v>65</v>
       </c>
       <c r="F39" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -2179,7 +2276,7 @@
         <v>66</v>
       </c>
       <c r="F40" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -2199,7 +2296,7 @@
         <v>67</v>
       </c>
       <c r="F41" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -2219,7 +2316,7 @@
         <v>68</v>
       </c>
       <c r="F42" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -2239,7 +2336,7 @@
         <v>69</v>
       </c>
       <c r="F43" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -2259,7 +2356,7 @@
         <v>70</v>
       </c>
       <c r="F44" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -2279,7 +2376,7 @@
         <v>71</v>
       </c>
       <c r="F45" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -2299,7 +2396,7 @@
         <v>72</v>
       </c>
       <c r="F46" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -2319,7 +2416,7 @@
         <v>73</v>
       </c>
       <c r="F47" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -2339,7 +2436,7 @@
         <v>74</v>
       </c>
       <c r="F48" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -2359,7 +2456,7 @@
         <v>75</v>
       </c>
       <c r="F49" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -2379,7 +2476,7 @@
         <v>76</v>
       </c>
       <c r="F50" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -2399,7 +2496,7 @@
         <v>70</v>
       </c>
       <c r="F51" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -2419,7 +2516,7 @@
         <v>71</v>
       </c>
       <c r="F52" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -2439,7 +2536,7 @@
         <v>77</v>
       </c>
       <c r="F53" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -2459,7 +2556,7 @@
         <v>75</v>
       </c>
       <c r="F54" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -2479,7 +2576,7 @@
         <v>78</v>
       </c>
       <c r="F55" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -2499,7 +2596,7 @@
         <v>79</v>
       </c>
       <c r="F56" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -2519,7 +2616,7 @@
         <v>80</v>
       </c>
       <c r="F57" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -2539,7 +2636,7 @@
         <v>81</v>
       </c>
       <c r="F58" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -2559,7 +2656,7 @@
         <v>82</v>
       </c>
       <c r="F59" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -2579,7 +2676,7 @@
         <v>83</v>
       </c>
       <c r="F60" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -2599,7 +2696,7 @@
         <v>84</v>
       </c>
       <c r="F61" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -2619,7 +2716,7 @@
         <v>85</v>
       </c>
       <c r="F62" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -2639,7 +2736,7 @@
         <v>86</v>
       </c>
       <c r="F63" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -2659,7 +2756,7 @@
         <v>87</v>
       </c>
       <c r="F64" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -2679,7 +2776,7 @@
         <v>88</v>
       </c>
       <c r="F65" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -2699,7 +2796,7 @@
         <v>89</v>
       </c>
       <c r="F66" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -2719,7 +2816,7 @@
         <v>90</v>
       </c>
       <c r="F67" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -2739,7 +2836,7 @@
         <v>91</v>
       </c>
       <c r="F68" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -2759,7 +2856,7 @@
         <v>92</v>
       </c>
       <c r="F69" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -2779,7 +2876,7 @@
         <v>93</v>
       </c>
       <c r="F70" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -2799,7 +2896,7 @@
         <v>94</v>
       </c>
       <c r="F71" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -2819,7 +2916,7 @@
         <v>88</v>
       </c>
       <c r="F72" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -2839,27 +2936,27 @@
         <v>95</v>
       </c>
       <c r="F73" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B74" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C74" s="2">
-        <v>46023</v>
+        <v>46030</v>
       </c>
       <c r="D74" s="2">
-        <v>46053</v>
+        <v>46036</v>
       </c>
       <c r="E74" t="s">
         <v>96</v>
       </c>
       <c r="F74" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -2870,16 +2967,16 @@
         <v>25</v>
       </c>
       <c r="C75" s="2">
-        <v>46030</v>
+        <v>46037</v>
       </c>
       <c r="D75" s="2">
-        <v>46036</v>
+        <v>46043</v>
       </c>
       <c r="E75" t="s">
         <v>97</v>
       </c>
       <c r="F75" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -2899,7 +2996,7 @@
         <v>98</v>
       </c>
       <c r="F76" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -2907,7 +3004,7 @@
         <v>8</v>
       </c>
       <c r="B77" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C77" s="2">
         <v>46037</v>
@@ -2919,67 +3016,67 @@
         <v>99</v>
       </c>
       <c r="F77" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B78" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C78" s="2">
-        <v>46037</v>
+        <v>46044</v>
       </c>
       <c r="D78" s="2">
-        <v>46043</v>
+        <v>46053</v>
       </c>
       <c r="E78" t="s">
         <v>100</v>
       </c>
       <c r="F78" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="79" spans="1:6">
       <c r="A79" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B79" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C79" s="2">
-        <v>46044</v>
+        <v>46054</v>
       </c>
       <c r="D79" s="2">
-        <v>46053</v>
+        <v>46060</v>
       </c>
       <c r="E79" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F79" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="80" spans="1:6">
       <c r="A80" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B80" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C80" s="2">
         <v>46054</v>
       </c>
       <c r="D80" s="2">
-        <v>46060</v>
+        <v>46081</v>
       </c>
       <c r="E80" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F80" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -2987,7 +3084,7 @@
         <v>7</v>
       </c>
       <c r="B81" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C81" s="2">
         <v>46054</v>
@@ -2999,7 +3096,7 @@
         <v>102</v>
       </c>
       <c r="F81" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -3007,7 +3104,7 @@
         <v>7</v>
       </c>
       <c r="B82" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C82" s="2">
         <v>46054</v>
@@ -3019,7 +3116,7 @@
         <v>103</v>
       </c>
       <c r="F82" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -3027,7 +3124,7 @@
         <v>7</v>
       </c>
       <c r="B83" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C83" s="2">
         <v>46054</v>
@@ -3039,7 +3136,7 @@
         <v>104</v>
       </c>
       <c r="F83" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -3047,7 +3144,7 @@
         <v>7</v>
       </c>
       <c r="B84" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C84" s="2">
         <v>46054</v>
@@ -3059,7 +3156,7 @@
         <v>105</v>
       </c>
       <c r="F84" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -3067,7 +3164,7 @@
         <v>7</v>
       </c>
       <c r="B85" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C85" s="2">
         <v>46054</v>
@@ -3079,27 +3176,27 @@
         <v>106</v>
       </c>
       <c r="F85" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="86" spans="1:6">
       <c r="A86" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B86" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C86" s="2">
-        <v>46054</v>
+        <v>46068</v>
       </c>
       <c r="D86" s="2">
-        <v>46081</v>
+        <v>46074</v>
       </c>
       <c r="E86" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="F86" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -3107,7 +3204,7 @@
         <v>8</v>
       </c>
       <c r="B87" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C87" s="2">
         <v>46068</v>
@@ -3116,10 +3213,10 @@
         <v>46074</v>
       </c>
       <c r="E87" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="F87" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -3130,36 +3227,36 @@
         <v>24</v>
       </c>
       <c r="C88" s="2">
-        <v>46068</v>
+        <v>46082</v>
       </c>
       <c r="D88" s="2">
-        <v>46074</v>
+        <v>46088</v>
       </c>
       <c r="E88" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="F88" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="89" spans="1:6">
       <c r="A89" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B89" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C89" s="2">
         <v>46082</v>
       </c>
       <c r="D89" s="2">
-        <v>46088</v>
+        <v>46112</v>
       </c>
       <c r="E89" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="F89" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -3167,7 +3264,7 @@
         <v>7</v>
       </c>
       <c r="B90" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C90" s="2">
         <v>46082</v>
@@ -3179,7 +3276,7 @@
         <v>108</v>
       </c>
       <c r="F90" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -3187,7 +3284,7 @@
         <v>7</v>
       </c>
       <c r="B91" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C91" s="2">
         <v>46082</v>
@@ -3199,7 +3296,7 @@
         <v>109</v>
       </c>
       <c r="F91" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -3207,7 +3304,7 @@
         <v>7</v>
       </c>
       <c r="B92" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C92" s="2">
         <v>46082</v>
@@ -3219,7 +3316,7 @@
         <v>110</v>
       </c>
       <c r="F92" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -3227,7 +3324,7 @@
         <v>7</v>
       </c>
       <c r="B93" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C93" s="2">
         <v>46082</v>
@@ -3239,35 +3336,35 @@
         <v>111</v>
       </c>
       <c r="F93" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="94" spans="1:6">
       <c r="A94" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B94" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C94" s="2">
-        <v>46096</v>
+        <v>46082</v>
       </c>
       <c r="D94" s="2">
-        <v>46102</v>
+        <v>46112</v>
       </c>
       <c r="E94" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="F94" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
     </row>
     <row r="95" spans="1:6">
       <c r="A95" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B95" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C95" s="2">
         <v>46096</v>
@@ -3276,90 +3373,90 @@
         <v>46102</v>
       </c>
       <c r="E95" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="F95" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="96" spans="1:6">
       <c r="A96" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B96" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C96" s="2">
-        <v>46113</v>
+        <v>46096</v>
       </c>
       <c r="D96" s="2">
-        <v>46119</v>
+        <v>46102</v>
       </c>
       <c r="E96" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="F96" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B97" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C97" s="2">
-        <v>46113</v>
+        <v>46103</v>
       </c>
       <c r="D97" s="2">
-        <v>46119</v>
+        <v>46112</v>
       </c>
       <c r="E97" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="F97" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B98" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C98" s="2">
         <v>46113</v>
       </c>
       <c r="D98" s="2">
-        <v>46142</v>
+        <v>46119</v>
       </c>
       <c r="E98" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="F98" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B99" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C99" s="2">
         <v>46113</v>
       </c>
       <c r="D99" s="2">
-        <v>46142</v>
+        <v>46119</v>
       </c>
       <c r="E99" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="F99" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="100" spans="1:6">
@@ -3367,7 +3464,7 @@
         <v>7</v>
       </c>
       <c r="B100" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C100" s="2">
         <v>46113</v>
@@ -3379,87 +3476,87 @@
         <v>115</v>
       </c>
       <c r="F100" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="101" spans="1:6">
       <c r="A101" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B101" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="C101" s="2">
         <v>46113</v>
       </c>
       <c r="D101" s="2">
-        <v>46119</v>
+        <v>46142</v>
       </c>
       <c r="E101" t="s">
         <v>116</v>
       </c>
       <c r="F101" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
     </row>
     <row r="102" spans="1:6">
       <c r="A102" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B102" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C102" s="2">
-        <v>46120</v>
+        <v>46113</v>
       </c>
       <c r="D102" s="2">
-        <v>46126</v>
+        <v>46142</v>
       </c>
       <c r="E102" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="F102" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
     </row>
     <row r="103" spans="1:6">
       <c r="A103" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B103" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C103" s="2">
-        <v>46120</v>
+        <v>46113</v>
       </c>
       <c r="D103" s="2">
-        <v>46126</v>
+        <v>46142</v>
       </c>
       <c r="E103" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F103" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
     </row>
     <row r="104" spans="1:6">
       <c r="A104" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B104" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C104" s="2">
-        <v>46127</v>
+        <v>46113</v>
       </c>
       <c r="D104" s="2">
-        <v>46133</v>
+        <v>46119</v>
       </c>
       <c r="E104" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F104" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="105" spans="1:6">
@@ -3467,39 +3564,39 @@
         <v>8</v>
       </c>
       <c r="B105" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C105" s="2">
-        <v>46134</v>
+        <v>46120</v>
       </c>
       <c r="D105" s="2">
-        <v>46142</v>
+        <v>46126</v>
       </c>
       <c r="E105" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="F105" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="106" spans="1:6">
       <c r="A106" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B106" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C106" s="2">
-        <v>46134</v>
+        <v>46120</v>
       </c>
       <c r="D106" s="2">
-        <v>46142</v>
+        <v>46126</v>
       </c>
       <c r="E106" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="F106" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="107" spans="1:6">
@@ -3510,76 +3607,76 @@
         <v>24</v>
       </c>
       <c r="C107" s="2">
-        <v>46134</v>
+        <v>46127</v>
       </c>
       <c r="D107" s="2">
-        <v>46142</v>
+        <v>46133</v>
       </c>
       <c r="E107" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="F107" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B108" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C108" s="2">
-        <v>46143</v>
+        <v>46134</v>
       </c>
       <c r="D108" s="2">
-        <v>46173</v>
+        <v>46142</v>
       </c>
       <c r="E108" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F108" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B109" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C109" s="2">
-        <v>46143</v>
+        <v>46134</v>
       </c>
       <c r="D109" s="2">
-        <v>46173</v>
+        <v>46142</v>
       </c>
       <c r="E109" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="F109" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="110" spans="1:6">
       <c r="A110" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B110" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C110" s="2">
-        <v>46143</v>
+        <v>46134</v>
       </c>
       <c r="D110" s="2">
-        <v>46173</v>
+        <v>46142</v>
       </c>
       <c r="E110" t="s">
-        <v>122</v>
+        <v>94</v>
       </c>
       <c r="F110" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="111" spans="1:6">
@@ -3587,7 +3684,7 @@
         <v>7</v>
       </c>
       <c r="B111" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C111" s="2">
         <v>46143</v>
@@ -3599,7 +3696,7 @@
         <v>123</v>
       </c>
       <c r="F111" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="112" spans="1:6">
@@ -3607,7 +3704,7 @@
         <v>7</v>
       </c>
       <c r="B112" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C112" s="2">
         <v>46143</v>
@@ -3619,7 +3716,7 @@
         <v>124</v>
       </c>
       <c r="F112" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -3627,7 +3724,7 @@
         <v>7</v>
       </c>
       <c r="B113" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C113" s="2">
         <v>46143</v>
@@ -3639,38 +3736,38 @@
         <v>125</v>
       </c>
       <c r="F113" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="114" spans="1:6">
       <c r="A114" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B114" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C114" s="2">
-        <v>46157</v>
+        <v>46143</v>
       </c>
       <c r="D114" s="2">
-        <v>46163</v>
+        <v>46173</v>
       </c>
       <c r="E114" t="s">
         <v>126</v>
       </c>
       <c r="F114" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B115" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C115" s="2">
-        <v>46164</v>
+        <v>46143</v>
       </c>
       <c r="D115" s="2">
         <v>46173</v>
@@ -3679,7 +3776,7 @@
         <v>127</v>
       </c>
       <c r="F115" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
     </row>
     <row r="116" spans="1:6">
@@ -3687,19 +3784,19 @@
         <v>7</v>
       </c>
       <c r="B116" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C116" s="2">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="D116" s="2">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="E116" t="s">
         <v>128</v>
       </c>
       <c r="F116" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -3707,59 +3804,59 @@
         <v>7</v>
       </c>
       <c r="B117" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C117" s="2">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="D117" s="2">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="E117" t="s">
         <v>129</v>
       </c>
       <c r="F117" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="118" spans="1:6">
       <c r="A118" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B118" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C118" s="2">
-        <v>46174</v>
+        <v>46157</v>
       </c>
       <c r="D118" s="2">
-        <v>46203</v>
+        <v>46163</v>
       </c>
       <c r="E118" t="s">
         <v>130</v>
       </c>
       <c r="F118" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="119" spans="1:6">
       <c r="A119" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B119" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C119" s="2">
-        <v>46174</v>
+        <v>46164</v>
       </c>
       <c r="D119" s="2">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="E119" t="s">
         <v>131</v>
       </c>
       <c r="F119" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -3767,7 +3864,7 @@
         <v>7</v>
       </c>
       <c r="B120" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C120" s="2">
         <v>46174</v>
@@ -3779,47 +3876,47 @@
         <v>132</v>
       </c>
       <c r="F120" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="121" spans="1:6">
       <c r="A121" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B121" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C121" s="2">
-        <v>46188</v>
+        <v>46174</v>
       </c>
       <c r="D121" s="2">
-        <v>46194</v>
+        <v>46203</v>
       </c>
       <c r="E121" t="s">
         <v>133</v>
       </c>
       <c r="F121" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
     </row>
     <row r="122" spans="1:6">
       <c r="A122" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B122" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C122" s="2">
-        <v>46204</v>
+        <v>46174</v>
       </c>
       <c r="D122" s="2">
-        <v>46210</v>
+        <v>46203</v>
       </c>
       <c r="E122" t="s">
-        <v>100</v>
+        <v>134</v>
       </c>
       <c r="F122" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -3827,19 +3924,19 @@
         <v>7</v>
       </c>
       <c r="B123" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C123" s="2">
-        <v>46204</v>
+        <v>46174</v>
       </c>
       <c r="D123" s="2">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="E123" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F123" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -3847,19 +3944,19 @@
         <v>7</v>
       </c>
       <c r="B124" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C124" s="2">
-        <v>46204</v>
+        <v>46174</v>
       </c>
       <c r="D124" s="2">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="E124" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F124" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="125" spans="1:6">
@@ -3867,139 +3964,139 @@
         <v>7</v>
       </c>
       <c r="B125" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C125" s="2">
-        <v>46204</v>
+        <v>46174</v>
       </c>
       <c r="D125" s="2">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="E125" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F125" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="126" spans="1:6">
       <c r="A126" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B126" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="C126" s="2">
-        <v>46204</v>
+        <v>46188</v>
       </c>
       <c r="D126" s="2">
-        <v>46234</v>
+        <v>46194</v>
       </c>
       <c r="E126" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F126" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="127" spans="1:6">
       <c r="A127" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B127" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C127" s="2">
-        <v>46204</v>
+        <v>46195</v>
       </c>
       <c r="D127" s="2">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="E127" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F127" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="128" spans="1:6">
       <c r="A128" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B128" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C128" s="2">
-        <v>46211</v>
+        <v>46204</v>
       </c>
       <c r="D128" s="2">
-        <v>46217</v>
+        <v>46210</v>
       </c>
       <c r="E128" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
       <c r="F128" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="129" spans="1:6">
       <c r="A129" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B129" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C129" s="2">
-        <v>46225</v>
+        <v>46204</v>
       </c>
       <c r="D129" s="2">
-        <v>46234</v>
+        <v>46210</v>
       </c>
       <c r="E129" t="s">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="F129" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="130" spans="1:6">
       <c r="A130" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B130" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C130" s="2">
-        <v>46225</v>
+        <v>46204</v>
       </c>
       <c r="D130" s="2">
         <v>46234</v>
       </c>
       <c r="E130" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F130" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
     </row>
     <row r="131" spans="1:6">
       <c r="A131" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B131" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C131" s="2">
-        <v>46225</v>
+        <v>46204</v>
       </c>
       <c r="D131" s="2">
         <v>46234</v>
       </c>
       <c r="E131" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F131" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -4007,99 +4104,99 @@
         <v>7</v>
       </c>
       <c r="B132" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C132" s="2">
-        <v>46235</v>
+        <v>46204</v>
       </c>
       <c r="D132" s="2">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="E132" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F132" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="133" spans="1:6">
       <c r="A133" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B133" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="C133" s="2">
-        <v>46235</v>
+        <v>46204</v>
       </c>
       <c r="D133" s="2">
-        <v>46265</v>
+        <v>46210</v>
       </c>
       <c r="E133" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F133" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="134" spans="1:6">
       <c r="A134" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B134" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="C134" s="2">
-        <v>46235</v>
+        <v>46211</v>
       </c>
       <c r="D134" s="2">
-        <v>46265</v>
+        <v>46217</v>
       </c>
       <c r="E134" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="F134" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="135" spans="1:6">
       <c r="A135" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B135" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C135" s="2">
-        <v>46235</v>
+        <v>46218</v>
       </c>
       <c r="D135" s="2">
-        <v>46265</v>
+        <v>46224</v>
       </c>
       <c r="E135" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F135" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="136" spans="1:6">
       <c r="A136" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B136" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C136" s="2">
-        <v>46242</v>
+        <v>46218</v>
       </c>
       <c r="D136" s="2">
-        <v>46248</v>
+        <v>46224</v>
       </c>
       <c r="E136" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="F136" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -4107,159 +4204,159 @@
         <v>8</v>
       </c>
       <c r="B137" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C137" s="2">
-        <v>46256</v>
+        <v>46225</v>
       </c>
       <c r="D137" s="2">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="E137" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="F137" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="138" spans="1:6">
       <c r="A138" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B138" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C138" s="2">
-        <v>46256</v>
+        <v>46225</v>
       </c>
       <c r="D138" s="2">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="E138" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F138" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="139" spans="1:6">
       <c r="A139" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B139" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C139" s="2">
-        <v>46266</v>
+        <v>46225</v>
       </c>
       <c r="D139" s="2">
-        <v>46272</v>
+        <v>46234</v>
       </c>
       <c r="E139" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="F139" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="140" spans="1:6">
       <c r="A140" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B140" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C140" s="2">
-        <v>46266</v>
+        <v>46232</v>
       </c>
       <c r="D140" s="2">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="E140" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="F140" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="A141" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B141" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="C141" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
       <c r="D141" s="2">
-        <v>46295</v>
+        <v>46241</v>
       </c>
       <c r="E141" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F141" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="142" spans="1:6">
       <c r="A142" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B142" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C142" s="2">
-        <v>46273</v>
+        <v>46235</v>
       </c>
       <c r="D142" s="2">
-        <v>46279</v>
+        <v>46265</v>
       </c>
       <c r="E142" t="s">
-        <v>100</v>
+        <v>147</v>
       </c>
       <c r="F142" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
     </row>
     <row r="143" spans="1:6">
       <c r="A143" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B143" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C143" s="2">
-        <v>46273</v>
+        <v>46235</v>
       </c>
       <c r="D143" s="2">
-        <v>46279</v>
+        <v>46265</v>
       </c>
       <c r="E143" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F143" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
     </row>
     <row r="144" spans="1:6">
       <c r="A144" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B144" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="C144" s="2">
-        <v>46273</v>
+        <v>46235</v>
       </c>
       <c r="D144" s="2">
-        <v>46279</v>
+        <v>46265</v>
       </c>
       <c r="E144" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F144" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -4267,19 +4364,19 @@
         <v>7</v>
       </c>
       <c r="B145" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C145" s="2">
-        <v>46296</v>
+        <v>46235</v>
       </c>
       <c r="D145" s="2">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="E145" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F145" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="146" spans="1:6">
@@ -4287,19 +4384,19 @@
         <v>7</v>
       </c>
       <c r="B146" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C146" s="2">
-        <v>46296</v>
+        <v>46235</v>
       </c>
       <c r="D146" s="2">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="E146" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F146" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -4310,76 +4407,76 @@
         <v>29</v>
       </c>
       <c r="C147" s="2">
-        <v>46296</v>
+        <v>46235</v>
       </c>
       <c r="D147" s="2">
-        <v>46302</v>
+        <v>46241</v>
       </c>
       <c r="E147" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="F147" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="148" spans="1:6">
       <c r="A148" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B148" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C148" s="2">
-        <v>46303</v>
+        <v>46242</v>
       </c>
       <c r="D148" s="2">
-        <v>46309</v>
+        <v>46248</v>
       </c>
       <c r="E148" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F148" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="149" spans="1:6">
       <c r="A149" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B149" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C149" s="2">
-        <v>46310</v>
+        <v>46242</v>
       </c>
       <c r="D149" s="2">
-        <v>46316</v>
+        <v>46248</v>
       </c>
       <c r="E149" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="F149" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="150" spans="1:6">
       <c r="A150" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B150" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C150" s="2">
-        <v>46317</v>
+        <v>46249</v>
       </c>
       <c r="D150" s="2">
-        <v>46326</v>
+        <v>46255</v>
       </c>
       <c r="E150" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="F150" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="151" spans="1:6">
@@ -4387,59 +4484,59 @@
         <v>8</v>
       </c>
       <c r="B151" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C151" s="2">
-        <v>46327</v>
+        <v>46256</v>
       </c>
       <c r="D151" s="2">
-        <v>46333</v>
+        <v>46265</v>
       </c>
       <c r="E151" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="F151" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="152" spans="1:6">
       <c r="A152" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B152" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C152" s="2">
-        <v>46327</v>
+        <v>46256</v>
       </c>
       <c r="D152" s="2">
-        <v>46333</v>
+        <v>46265</v>
       </c>
       <c r="E152" t="s">
-        <v>94</v>
+        <v>154</v>
       </c>
       <c r="F152" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="153" spans="1:6">
       <c r="A153" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B153" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C153" s="2">
-        <v>46327</v>
+        <v>46266</v>
       </c>
       <c r="D153" s="2">
-        <v>46356</v>
+        <v>46272</v>
       </c>
       <c r="E153" t="s">
-        <v>157</v>
+        <v>99</v>
       </c>
       <c r="F153" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -4447,59 +4544,59 @@
         <v>7</v>
       </c>
       <c r="B154" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C154" s="2">
-        <v>46327</v>
+        <v>46266</v>
       </c>
       <c r="D154" s="2">
-        <v>46356</v>
+        <v>46295</v>
       </c>
       <c r="E154" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F154" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="155" spans="1:6">
       <c r="A155" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B155" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C155" s="2">
-        <v>46334</v>
+        <v>46266</v>
       </c>
       <c r="D155" s="2">
-        <v>46340</v>
+        <v>46295</v>
       </c>
       <c r="E155" t="s">
-        <v>94</v>
+        <v>156</v>
       </c>
       <c r="F155" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
     </row>
     <row r="156" spans="1:6">
       <c r="A156" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B156" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C156" s="2">
-        <v>46334</v>
+        <v>46273</v>
       </c>
       <c r="D156" s="2">
-        <v>46340</v>
+        <v>46279</v>
       </c>
       <c r="E156" t="s">
-        <v>159</v>
+        <v>99</v>
       </c>
       <c r="F156" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="157" spans="1:6">
@@ -4510,56 +4607,56 @@
         <v>30</v>
       </c>
       <c r="C157" s="2">
-        <v>46341</v>
+        <v>46273</v>
       </c>
       <c r="D157" s="2">
-        <v>46347</v>
+        <v>46279</v>
       </c>
       <c r="E157" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F157" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="158" spans="1:6">
       <c r="A158" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B158" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C158" s="2">
-        <v>46357</v>
+        <v>46280</v>
       </c>
       <c r="D158" s="2">
-        <v>46363</v>
+        <v>46286</v>
       </c>
       <c r="E158" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F158" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="159" spans="1:6">
       <c r="A159" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B159" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C159" s="2">
-        <v>46357</v>
+        <v>46296</v>
       </c>
       <c r="D159" s="2">
-        <v>46363</v>
+        <v>46326</v>
       </c>
       <c r="E159" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F159" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
     </row>
     <row r="160" spans="1:6">
@@ -4567,19 +4664,19 @@
         <v>7</v>
       </c>
       <c r="B160" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C160" s="2">
-        <v>46357</v>
+        <v>46296</v>
       </c>
       <c r="D160" s="2">
-        <v>46387</v>
+        <v>46326</v>
       </c>
       <c r="E160" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F160" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="161" spans="1:6">
@@ -4587,39 +4684,39 @@
         <v>7</v>
       </c>
       <c r="B161" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C161" s="2">
-        <v>46357</v>
+        <v>46296</v>
       </c>
       <c r="D161" s="2">
-        <v>46387</v>
+        <v>46326</v>
       </c>
       <c r="E161" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F161" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="162" spans="1:6">
       <c r="A162" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B162" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C162" s="2">
-        <v>46357</v>
+        <v>46296</v>
       </c>
       <c r="D162" s="2">
-        <v>46363</v>
+        <v>46326</v>
       </c>
       <c r="E162" t="s">
-        <v>165</v>
+        <v>97</v>
       </c>
       <c r="F162" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
     </row>
     <row r="163" spans="1:6">
@@ -4630,16 +4727,16 @@
         <v>26</v>
       </c>
       <c r="C163" s="2">
-        <v>46364</v>
+        <v>46310</v>
       </c>
       <c r="D163" s="2">
-        <v>46370</v>
+        <v>46316</v>
       </c>
       <c r="E163" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="F163" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="164" spans="1:6">
@@ -4650,16 +4747,16 @@
         <v>27</v>
       </c>
       <c r="C164" s="2">
-        <v>46364</v>
+        <v>46310</v>
       </c>
       <c r="D164" s="2">
-        <v>46370</v>
+        <v>46316</v>
       </c>
       <c r="E164" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="F164" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="165" spans="1:6">
@@ -4670,336 +4767,336 @@
         <v>25</v>
       </c>
       <c r="C165" s="2">
-        <v>46371</v>
+        <v>46317</v>
       </c>
       <c r="D165" s="2">
-        <v>46377</v>
+        <v>46326</v>
       </c>
       <c r="E165" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F165" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="166" spans="1:6">
       <c r="A166" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B166" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C166" s="2">
-        <v>46388</v>
+        <v>46327</v>
       </c>
       <c r="D166" s="2">
-        <v>46394</v>
+        <v>46333</v>
       </c>
       <c r="E166" t="s">
-        <v>168</v>
+        <v>99</v>
       </c>
       <c r="F166" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="167" spans="1:6">
       <c r="A167" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B167" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C167" s="2">
-        <v>46388</v>
+        <v>46327</v>
       </c>
       <c r="D167" s="2">
-        <v>46394</v>
+        <v>46333</v>
       </c>
       <c r="E167" t="s">
-        <v>168</v>
+        <v>94</v>
       </c>
       <c r="F167" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="168" spans="1:6">
       <c r="A168" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B168" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="C168" s="2">
-        <v>46388</v>
+        <v>46327</v>
       </c>
       <c r="D168" s="2">
-        <v>46418</v>
+        <v>46356</v>
       </c>
       <c r="E168" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="F168" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="169" spans="1:6">
       <c r="A169" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B169" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C169" s="2">
-        <v>46388</v>
+        <v>46327</v>
       </c>
       <c r="D169" s="2">
-        <v>46418</v>
+        <v>46333</v>
       </c>
       <c r="E169" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="F169" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="170" spans="1:6">
       <c r="A170" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B170" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C170" s="2">
-        <v>46388</v>
+        <v>46334</v>
       </c>
       <c r="D170" s="2">
-        <v>46418</v>
+        <v>46340</v>
       </c>
       <c r="E170" t="s">
-        <v>171</v>
+        <v>94</v>
       </c>
       <c r="F170" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="171" spans="1:6">
       <c r="A171" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B171" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C171" s="2">
-        <v>46388</v>
+        <v>46334</v>
       </c>
       <c r="D171" s="2">
-        <v>46418</v>
+        <v>46340</v>
       </c>
       <c r="E171" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="F171" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="172" spans="1:6">
       <c r="A172" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B172" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C172" s="2">
-        <v>46388</v>
+        <v>46341</v>
       </c>
       <c r="D172" s="2">
-        <v>46418</v>
+        <v>46347</v>
       </c>
       <c r="E172" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="F172" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="173" spans="1:6">
       <c r="A173" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B173" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C173" s="2">
-        <v>46388</v>
+        <v>46357</v>
       </c>
       <c r="D173" s="2">
-        <v>46418</v>
+        <v>46363</v>
       </c>
       <c r="E173" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="F173" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="174" spans="1:6">
       <c r="A174" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B174" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C174" s="2">
-        <v>46388</v>
+        <v>46357</v>
       </c>
       <c r="D174" s="2">
-        <v>46418</v>
+        <v>46363</v>
       </c>
       <c r="E174" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="F174" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="175" spans="1:6">
       <c r="A175" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B175" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="C175" s="2">
-        <v>46388</v>
+        <v>46357</v>
       </c>
       <c r="D175" s="2">
-        <v>46418</v>
+        <v>46387</v>
       </c>
       <c r="E175" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="F175" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="176" spans="1:6">
       <c r="A176" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B176" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C176" s="2">
-        <v>46388</v>
+        <v>46364</v>
       </c>
       <c r="D176" s="2">
-        <v>46418</v>
+        <v>46370</v>
       </c>
       <c r="E176" t="s">
-        <v>177</v>
+        <v>94</v>
       </c>
       <c r="F176" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="177" spans="1:6">
       <c r="A177" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B177" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C177" s="2">
-        <v>46395</v>
+        <v>46364</v>
       </c>
       <c r="D177" s="2">
-        <v>46401</v>
+        <v>46370</v>
       </c>
       <c r="E177" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F177" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="178" spans="1:6">
       <c r="A178" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B178" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="C178" s="2">
-        <v>46409</v>
+        <v>46371</v>
       </c>
       <c r="D178" s="2">
-        <v>46418</v>
+        <v>46377</v>
       </c>
       <c r="E178" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="F178" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="179" spans="1:6">
       <c r="A179" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B179" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C179" s="2">
-        <v>46419</v>
+        <v>46388</v>
       </c>
       <c r="D179" s="2">
-        <v>46446</v>
+        <v>46394</v>
       </c>
       <c r="E179" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F179" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="180" spans="1:6">
       <c r="A180" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B180" t="s">
         <v>32</v>
       </c>
       <c r="C180" s="2">
-        <v>46419</v>
+        <v>46388</v>
       </c>
       <c r="D180" s="2">
-        <v>46446</v>
+        <v>46394</v>
       </c>
       <c r="E180" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F180" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="181" spans="1:6">
       <c r="A181" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B181" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="C181" s="2">
-        <v>46419</v>
+        <v>46388</v>
       </c>
       <c r="D181" s="2">
-        <v>46446</v>
+        <v>46418</v>
       </c>
       <c r="E181" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="F181" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="182" spans="1:6">
@@ -5007,19 +5104,19 @@
         <v>13</v>
       </c>
       <c r="B182" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C182" s="2">
-        <v>46419</v>
+        <v>46388</v>
       </c>
       <c r="D182" s="2">
-        <v>46446</v>
+        <v>46418</v>
       </c>
       <c r="E182" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="F182" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="183" spans="1:6">
@@ -5027,59 +5124,59 @@
         <v>13</v>
       </c>
       <c r="B183" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C183" s="2">
-        <v>46419</v>
+        <v>46388</v>
       </c>
       <c r="D183" s="2">
-        <v>46446</v>
+        <v>46418</v>
       </c>
       <c r="E183" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="F183" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="184" spans="1:6">
       <c r="A184" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B184" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C184" s="2">
-        <v>46426</v>
+        <v>46388</v>
       </c>
       <c r="D184" s="2">
-        <v>46432</v>
+        <v>46418</v>
       </c>
       <c r="E184" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="F184" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
     </row>
     <row r="185" spans="1:6">
       <c r="A185" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B185" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C185" s="2">
-        <v>46440</v>
+        <v>46388</v>
       </c>
       <c r="D185" s="2">
-        <v>46446</v>
+        <v>46418</v>
       </c>
       <c r="E185" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="F185" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
     </row>
     <row r="186" spans="1:6">
@@ -5087,19 +5184,19 @@
         <v>12</v>
       </c>
       <c r="B186" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C186" s="2">
-        <v>46447</v>
+        <v>46395</v>
       </c>
       <c r="D186" s="2">
-        <v>46453</v>
+        <v>46401</v>
       </c>
       <c r="E186" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="F186" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="187" spans="1:6">
@@ -5107,39 +5204,39 @@
         <v>12</v>
       </c>
       <c r="B187" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C187" s="2">
-        <v>46447</v>
+        <v>46409</v>
       </c>
       <c r="D187" s="2">
-        <v>46453</v>
+        <v>46418</v>
       </c>
       <c r="E187" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="F187" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="188" spans="1:6">
       <c r="A188" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B188" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="C188" s="2">
-        <v>46447</v>
+        <v>46419</v>
       </c>
       <c r="D188" s="2">
-        <v>46477</v>
+        <v>46446</v>
       </c>
       <c r="E188" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="F188" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="189" spans="1:6">
@@ -5147,19 +5244,19 @@
         <v>13</v>
       </c>
       <c r="B189" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C189" s="2">
-        <v>46447</v>
+        <v>46419</v>
       </c>
       <c r="D189" s="2">
-        <v>46477</v>
+        <v>46446</v>
       </c>
       <c r="E189" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="F189" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="190" spans="1:6">
@@ -5167,19 +5264,19 @@
         <v>13</v>
       </c>
       <c r="B190" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C190" s="2">
-        <v>46447</v>
+        <v>46419</v>
       </c>
       <c r="D190" s="2">
-        <v>46477</v>
+        <v>46446</v>
       </c>
       <c r="E190" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="F190" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="191" spans="1:6">
@@ -5187,19 +5284,19 @@
         <v>13</v>
       </c>
       <c r="B191" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C191" s="2">
-        <v>46447</v>
+        <v>46419</v>
       </c>
       <c r="D191" s="2">
-        <v>46477</v>
+        <v>46446</v>
       </c>
       <c r="E191" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="F191" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="192" spans="1:6">
@@ -5207,19 +5304,19 @@
         <v>13</v>
       </c>
       <c r="B192" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C192" s="2">
-        <v>46447</v>
+        <v>46419</v>
       </c>
       <c r="D192" s="2">
-        <v>46477</v>
+        <v>46446</v>
       </c>
       <c r="E192" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="F192" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="193" spans="1:6">
@@ -5227,19 +5324,19 @@
         <v>13</v>
       </c>
       <c r="B193" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C193" s="2">
-        <v>46447</v>
+        <v>46419</v>
       </c>
       <c r="D193" s="2">
-        <v>46477</v>
+        <v>46446</v>
       </c>
       <c r="E193" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="F193" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="194" spans="1:6">
@@ -5247,59 +5344,59 @@
         <v>13</v>
       </c>
       <c r="B194" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C194" s="2">
-        <v>46447</v>
+        <v>46419</v>
       </c>
       <c r="D194" s="2">
-        <v>46477</v>
+        <v>46446</v>
       </c>
       <c r="E194" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="F194" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="195" spans="1:6">
       <c r="A195" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B195" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C195" s="2">
-        <v>46447</v>
+        <v>46426</v>
       </c>
       <c r="D195" s="2">
-        <v>46477</v>
+        <v>46432</v>
       </c>
       <c r="E195" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="F195" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="196" spans="1:6">
       <c r="A196" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B196" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C196" s="2">
-        <v>46447</v>
+        <v>46440</v>
       </c>
       <c r="D196" s="2">
-        <v>46477</v>
+        <v>46446</v>
       </c>
       <c r="E196" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F196" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="197" spans="1:6">
@@ -5307,19 +5404,19 @@
         <v>14</v>
       </c>
       <c r="B197" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C197" s="2">
-        <v>46447</v>
+        <v>46440</v>
       </c>
       <c r="D197" s="2">
-        <v>46453</v>
+        <v>46446</v>
       </c>
       <c r="E197" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="F197" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="198" spans="1:6">
@@ -5327,19 +5424,19 @@
         <v>12</v>
       </c>
       <c r="B198" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C198" s="2">
-        <v>46454</v>
+        <v>46447</v>
       </c>
       <c r="D198" s="2">
-        <v>46460</v>
+        <v>46453</v>
       </c>
       <c r="E198" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F198" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="199" spans="1:6">
@@ -5347,79 +5444,79 @@
         <v>12</v>
       </c>
       <c r="B199" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C199" s="2">
-        <v>46461</v>
+        <v>46447</v>
       </c>
       <c r="D199" s="2">
-        <v>46467</v>
+        <v>46453</v>
       </c>
       <c r="E199" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="F199" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="200" spans="1:6">
       <c r="A200" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B200" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="C200" s="2">
-        <v>46478</v>
+        <v>46447</v>
       </c>
       <c r="D200" s="2">
-        <v>46484</v>
+        <v>46477</v>
       </c>
       <c r="E200" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="F200" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
     </row>
     <row r="201" spans="1:6">
       <c r="A201" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B201" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C201" s="2">
-        <v>46478</v>
+        <v>46447</v>
       </c>
       <c r="D201" s="2">
-        <v>46484</v>
+        <v>46477</v>
       </c>
       <c r="E201" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="F201" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
     </row>
     <row r="202" spans="1:6">
       <c r="A202" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B202" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C202" s="2">
-        <v>46478</v>
+        <v>46447</v>
       </c>
       <c r="D202" s="2">
-        <v>46484</v>
+        <v>46477</v>
       </c>
       <c r="E202" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="F202" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
     </row>
     <row r="203" spans="1:6">
@@ -5430,16 +5527,16 @@
         <v>34</v>
       </c>
       <c r="C203" s="2">
-        <v>46478</v>
+        <v>46447</v>
       </c>
       <c r="D203" s="2">
-        <v>46507</v>
+        <v>46477</v>
       </c>
       <c r="E203" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="F203" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="204" spans="1:6">
@@ -5447,87 +5544,87 @@
         <v>13</v>
       </c>
       <c r="B204" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C204" s="2">
-        <v>46478</v>
+        <v>46447</v>
       </c>
       <c r="D204" s="2">
-        <v>46507</v>
+        <v>46477</v>
       </c>
       <c r="E204" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="F204" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="205" spans="1:6">
       <c r="A205" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B205" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C205" s="2">
-        <v>46478</v>
+        <v>46447</v>
       </c>
       <c r="D205" s="2">
-        <v>46507</v>
+        <v>46453</v>
       </c>
       <c r="E205" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="F205" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="206" spans="1:6">
       <c r="A206" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B206" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C206" s="2">
         <v>46478</v>
       </c>
       <c r="D206" s="2">
-        <v>46507</v>
+        <v>46484</v>
       </c>
       <c r="E206" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="F206" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="207" spans="1:6">
       <c r="A207" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B207" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C207" s="2">
         <v>46478</v>
       </c>
       <c r="D207" s="2">
-        <v>46507</v>
+        <v>46484</v>
       </c>
       <c r="E207" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="F207" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="208" spans="1:6">
       <c r="A208" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B208" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C208" s="2">
         <v>46478</v>
@@ -5536,10 +5633,10 @@
         <v>46507</v>
       </c>
       <c r="E208" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F208" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="209" spans="1:6">
@@ -5556,10 +5653,10 @@
         <v>46507</v>
       </c>
       <c r="E209" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F209" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="210" spans="1:6">
@@ -5567,7 +5664,7 @@
         <v>13</v>
       </c>
       <c r="B210" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C210" s="2">
         <v>46478</v>
@@ -5576,15 +5673,15 @@
         <v>46507</v>
       </c>
       <c r="E210" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="F210" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="211" spans="1:6">
       <c r="A211" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B211" t="s">
         <v>40</v>
@@ -5593,233 +5690,233 @@
         <v>46478</v>
       </c>
       <c r="D211" s="2">
-        <v>46507</v>
+        <v>46484</v>
       </c>
       <c r="E211" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="F211" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="212" spans="1:6">
       <c r="A212" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B212" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C212" s="2">
-        <v>46478</v>
+        <v>46492</v>
       </c>
       <c r="D212" s="2">
-        <v>46507</v>
+        <v>46498</v>
       </c>
       <c r="E212" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="F212" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="213" spans="1:6">
       <c r="A213" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B213" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C213" s="2">
-        <v>46478</v>
+        <v>46499</v>
       </c>
       <c r="D213" s="2">
         <v>46507</v>
       </c>
       <c r="E213" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="F213" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="214" spans="1:6">
       <c r="A214" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B214" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C214" s="2">
-        <v>46478</v>
+        <v>46508</v>
       </c>
       <c r="D214" s="2">
-        <v>46507</v>
+        <v>46514</v>
       </c>
       <c r="E214" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="F214" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="215" spans="1:6">
       <c r="A215" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B215" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="C215" s="2">
-        <v>46478</v>
+        <v>46508</v>
       </c>
       <c r="D215" s="2">
-        <v>46507</v>
+        <v>46538</v>
       </c>
       <c r="E215" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="F215" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="216" spans="1:6">
       <c r="A216" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B216" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C216" s="2">
-        <v>46478</v>
+        <v>46508</v>
       </c>
       <c r="D216" s="2">
-        <v>46484</v>
+        <v>46538</v>
       </c>
       <c r="E216" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="F216" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
     </row>
     <row r="217" spans="1:6">
       <c r="A217" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B217" t="s">
         <v>32</v>
       </c>
       <c r="C217" s="2">
-        <v>46492</v>
+        <v>46508</v>
       </c>
       <c r="D217" s="2">
-        <v>46498</v>
+        <v>46538</v>
       </c>
       <c r="E217" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="F217" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
     </row>
     <row r="218" spans="1:6">
       <c r="A218" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B218" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C218" s="2">
         <v>46508</v>
       </c>
       <c r="D218" s="2">
-        <v>46514</v>
+        <v>46538</v>
       </c>
       <c r="E218" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="F218" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
     </row>
     <row r="219" spans="1:6">
       <c r="A219" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B219" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="C219" s="2">
-        <v>46508</v>
+        <v>46515</v>
       </c>
       <c r="D219" s="2">
-        <v>46538</v>
+        <v>46521</v>
       </c>
       <c r="E219" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="F219" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="220" spans="1:6">
       <c r="A220" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B220" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C220" s="2">
-        <v>46508</v>
+        <v>46522</v>
       </c>
       <c r="D220" s="2">
-        <v>46538</v>
+        <v>46528</v>
       </c>
       <c r="E220" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="F220" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="221" spans="1:6">
       <c r="A221" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B221" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C221" s="2">
-        <v>46508</v>
+        <v>46529</v>
       </c>
       <c r="D221" s="2">
         <v>46538</v>
       </c>
       <c r="E221" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F221" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="222" spans="1:6">
       <c r="A222" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B222" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="C222" s="2">
-        <v>46508</v>
+        <v>46539</v>
       </c>
       <c r="D222" s="2">
-        <v>46538</v>
+        <v>46568</v>
       </c>
       <c r="E222" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="F222" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="223" spans="1:6">
@@ -5827,19 +5924,19 @@
         <v>13</v>
       </c>
       <c r="B223" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C223" s="2">
-        <v>46508</v>
+        <v>46539</v>
       </c>
       <c r="D223" s="2">
-        <v>46538</v>
+        <v>46568</v>
       </c>
       <c r="E223" t="s">
-        <v>173</v>
+        <v>213</v>
       </c>
       <c r="F223" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="224" spans="1:6">
@@ -5847,19 +5944,19 @@
         <v>13</v>
       </c>
       <c r="B224" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C224" s="2">
-        <v>46508</v>
+        <v>46539</v>
       </c>
       <c r="D224" s="2">
-        <v>46538</v>
+        <v>46568</v>
       </c>
       <c r="E224" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="F224" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="225" spans="1:6">
@@ -5870,16 +5967,16 @@
         <v>38</v>
       </c>
       <c r="C225" s="2">
-        <v>46508</v>
+        <v>46539</v>
       </c>
       <c r="D225" s="2">
-        <v>46538</v>
+        <v>46568</v>
       </c>
       <c r="E225" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="F225" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="226" spans="1:6">
@@ -5887,79 +5984,79 @@
         <v>13</v>
       </c>
       <c r="B226" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C226" s="2">
-        <v>46508</v>
+        <v>46539</v>
       </c>
       <c r="D226" s="2">
-        <v>46538</v>
+        <v>46568</v>
       </c>
       <c r="E226" t="s">
-        <v>220</v>
+        <v>184</v>
       </c>
       <c r="F226" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="227" spans="1:6">
       <c r="A227" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B227" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C227" s="2">
-        <v>46515</v>
+        <v>46539</v>
       </c>
       <c r="D227" s="2">
-        <v>46521</v>
+        <v>46568</v>
       </c>
       <c r="E227" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="F227" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
     </row>
     <row r="228" spans="1:6">
       <c r="A228" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B228" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C228" s="2">
-        <v>46522</v>
+        <v>46539</v>
       </c>
       <c r="D228" s="2">
-        <v>46528</v>
+        <v>46568</v>
       </c>
       <c r="E228" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="F228" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
     </row>
     <row r="229" spans="1:6">
       <c r="A229" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B229" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C229" s="2">
-        <v>46529</v>
+        <v>46539</v>
       </c>
       <c r="D229" s="2">
-        <v>46538</v>
+        <v>46568</v>
       </c>
       <c r="E229" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="F229" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
     </row>
     <row r="230" spans="1:6">
@@ -5967,99 +6064,99 @@
         <v>12</v>
       </c>
       <c r="B230" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C230" s="2">
-        <v>46529</v>
+        <v>46546</v>
       </c>
       <c r="D230" s="2">
-        <v>46538</v>
+        <v>46552</v>
       </c>
       <c r="E230" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="F230" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="231" spans="1:6">
       <c r="A231" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B231" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="C231" s="2">
-        <v>46539</v>
+        <v>46560</v>
       </c>
       <c r="D231" s="2">
         <v>46568</v>
       </c>
       <c r="E231" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F231" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="232" spans="1:6">
       <c r="A232" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B232" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C232" s="2">
-        <v>46539</v>
+        <v>46569</v>
       </c>
       <c r="D232" s="2">
-        <v>46568</v>
+        <v>46575</v>
       </c>
       <c r="E232" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="F232" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="233" spans="1:6">
       <c r="A233" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B233" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C233" s="2">
-        <v>46539</v>
+        <v>46569</v>
       </c>
       <c r="D233" s="2">
-        <v>46568</v>
+        <v>46575</v>
       </c>
       <c r="E233" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="F233" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="234" spans="1:6">
       <c r="A234" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B234" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C234" s="2">
-        <v>46539</v>
+        <v>46569</v>
       </c>
       <c r="D234" s="2">
-        <v>46568</v>
+        <v>46599</v>
       </c>
       <c r="E234" t="s">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="F234" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="235" spans="1:6">
@@ -6067,19 +6164,19 @@
         <v>13</v>
       </c>
       <c r="B235" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C235" s="2">
-        <v>46539</v>
+        <v>46569</v>
       </c>
       <c r="D235" s="2">
-        <v>46568</v>
+        <v>46599</v>
       </c>
       <c r="E235" t="s">
-        <v>229</v>
+        <v>194</v>
       </c>
       <c r="F235" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="236" spans="1:6">
@@ -6087,19 +6184,19 @@
         <v>13</v>
       </c>
       <c r="B236" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C236" s="2">
-        <v>46539</v>
+        <v>46569</v>
       </c>
       <c r="D236" s="2">
-        <v>46568</v>
+        <v>46599</v>
       </c>
       <c r="E236" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="F236" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="237" spans="1:6">
@@ -6107,19 +6204,19 @@
         <v>13</v>
       </c>
       <c r="B237" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C237" s="2">
-        <v>46539</v>
+        <v>46569</v>
       </c>
       <c r="D237" s="2">
-        <v>46568</v>
+        <v>46599</v>
       </c>
       <c r="E237" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="F237" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="238" spans="1:6">
@@ -6127,99 +6224,99 @@
         <v>13</v>
       </c>
       <c r="B238" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C238" s="2">
-        <v>46539</v>
+        <v>46569</v>
       </c>
       <c r="D238" s="2">
-        <v>46568</v>
+        <v>46599</v>
       </c>
       <c r="E238" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="F238" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="239" spans="1:6">
       <c r="A239" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B239" t="s">
         <v>32</v>
       </c>
       <c r="C239" s="2">
-        <v>46539</v>
+        <v>46576</v>
       </c>
       <c r="D239" s="2">
-        <v>46568</v>
+        <v>46582</v>
       </c>
       <c r="E239" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="F239" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="240" spans="1:6">
       <c r="A240" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B240" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C240" s="2">
-        <v>46539</v>
+        <v>46583</v>
       </c>
       <c r="D240" s="2">
-        <v>46568</v>
+        <v>46589</v>
       </c>
       <c r="E240" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="F240" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="241" spans="1:6">
       <c r="A241" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B241" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C241" s="2">
-        <v>46539</v>
+        <v>46600</v>
       </c>
       <c r="D241" s="2">
-        <v>46568</v>
+        <v>46606</v>
       </c>
       <c r="E241" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="F241" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="242" spans="1:6">
       <c r="A242" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B242" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C242" s="2">
-        <v>46539</v>
+        <v>46600</v>
       </c>
       <c r="D242" s="2">
-        <v>46568</v>
+        <v>46606</v>
       </c>
       <c r="E242" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="F242" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="243" spans="1:6">
@@ -6227,19 +6324,19 @@
         <v>13</v>
       </c>
       <c r="B243" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C243" s="2">
-        <v>46539</v>
+        <v>46600</v>
       </c>
       <c r="D243" s="2">
-        <v>46568</v>
+        <v>46630</v>
       </c>
       <c r="E243" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="F243" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="244" spans="1:6">
@@ -6250,16 +6347,16 @@
         <v>38</v>
       </c>
       <c r="C244" s="2">
-        <v>46539</v>
+        <v>46600</v>
       </c>
       <c r="D244" s="2">
-        <v>46568</v>
+        <v>46630</v>
       </c>
       <c r="E244" t="s">
-        <v>237</v>
+        <v>194</v>
       </c>
       <c r="F244" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="245" spans="1:6">
@@ -6267,79 +6364,79 @@
         <v>13</v>
       </c>
       <c r="B245" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C245" s="2">
-        <v>46539</v>
+        <v>46600</v>
       </c>
       <c r="D245" s="2">
-        <v>46568</v>
+        <v>46630</v>
       </c>
       <c r="E245" t="s">
-        <v>238</v>
+        <v>184</v>
       </c>
       <c r="F245" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="246" spans="1:6">
       <c r="A246" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B246" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C246" s="2">
-        <v>46546</v>
+        <v>46600</v>
       </c>
       <c r="D246" s="2">
-        <v>46552</v>
+        <v>46630</v>
       </c>
       <c r="E246" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="F246" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
     </row>
     <row r="247" spans="1:6">
       <c r="A247" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B247" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C247" s="2">
-        <v>46560</v>
+        <v>46600</v>
       </c>
       <c r="D247" s="2">
-        <v>46568</v>
+        <v>46630</v>
       </c>
       <c r="E247" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="F247" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
     </row>
     <row r="248" spans="1:6">
       <c r="A248" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B248" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C248" s="2">
-        <v>46569</v>
+        <v>46600</v>
       </c>
       <c r="D248" s="2">
-        <v>46575</v>
+        <v>46630</v>
       </c>
       <c r="E248" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="F248" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
     </row>
     <row r="249" spans="1:6">
@@ -6347,79 +6444,79 @@
         <v>13</v>
       </c>
       <c r="B249" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C249" s="2">
-        <v>46569</v>
+        <v>46600</v>
       </c>
       <c r="D249" s="2">
-        <v>46599</v>
+        <v>46630</v>
       </c>
       <c r="E249" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="F249" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="250" spans="1:6">
       <c r="A250" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B250" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C250" s="2">
-        <v>46569</v>
+        <v>46607</v>
       </c>
       <c r="D250" s="2">
-        <v>46599</v>
+        <v>46613</v>
       </c>
       <c r="E250" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="F250" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="251" spans="1:6">
       <c r="A251" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B251" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C251" s="2">
-        <v>46569</v>
+        <v>46607</v>
       </c>
       <c r="D251" s="2">
-        <v>46599</v>
+        <v>46613</v>
       </c>
       <c r="E251" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="F251" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="252" spans="1:6">
       <c r="A252" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B252" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C252" s="2">
-        <v>46569</v>
+        <v>46631</v>
       </c>
       <c r="D252" s="2">
-        <v>46599</v>
+        <v>46637</v>
       </c>
       <c r="E252" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="F252" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="253" spans="1:6">
@@ -6427,19 +6524,19 @@
         <v>13</v>
       </c>
       <c r="B253" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C253" s="2">
-        <v>46569</v>
+        <v>46631</v>
       </c>
       <c r="D253" s="2">
-        <v>46599</v>
+        <v>46660</v>
       </c>
       <c r="E253" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="F253" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="254" spans="1:6">
@@ -6447,19 +6544,19 @@
         <v>13</v>
       </c>
       <c r="B254" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C254" s="2">
-        <v>46569</v>
+        <v>46631</v>
       </c>
       <c r="D254" s="2">
-        <v>46599</v>
+        <v>46660</v>
       </c>
       <c r="E254" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="F254" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="255" spans="1:6">
@@ -6467,19 +6564,19 @@
         <v>13</v>
       </c>
       <c r="B255" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C255" s="2">
-        <v>46569</v>
+        <v>46631</v>
       </c>
       <c r="D255" s="2">
-        <v>46599</v>
+        <v>46660</v>
       </c>
       <c r="E255" t="s">
-        <v>247</v>
+        <v>194</v>
       </c>
       <c r="F255" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="256" spans="1:6">
@@ -6487,19 +6584,19 @@
         <v>13</v>
       </c>
       <c r="B256" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C256" s="2">
-        <v>46569</v>
+        <v>46631</v>
       </c>
       <c r="D256" s="2">
-        <v>46599</v>
+        <v>46660</v>
       </c>
       <c r="E256" t="s">
-        <v>248</v>
+        <v>184</v>
       </c>
       <c r="F256" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="257" spans="1:6">
@@ -6507,19 +6604,19 @@
         <v>13</v>
       </c>
       <c r="B257" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C257" s="2">
-        <v>46569</v>
+        <v>46631</v>
       </c>
       <c r="D257" s="2">
-        <v>46599</v>
+        <v>46660</v>
       </c>
       <c r="E257" t="s">
-        <v>6</v>
+        <v>237</v>
       </c>
       <c r="F257" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="258" spans="1:6">
@@ -6527,19 +6624,19 @@
         <v>13</v>
       </c>
       <c r="B258" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C258" s="2">
-        <v>46569</v>
+        <v>46631</v>
       </c>
       <c r="D258" s="2">
-        <v>46599</v>
+        <v>46660</v>
       </c>
       <c r="E258" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F258" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="259" spans="1:6">
@@ -6547,59 +6644,59 @@
         <v>13</v>
       </c>
       <c r="B259" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C259" s="2">
-        <v>46569</v>
+        <v>46631</v>
       </c>
       <c r="D259" s="2">
-        <v>46599</v>
+        <v>46660</v>
       </c>
       <c r="E259" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F259" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="260" spans="1:6">
       <c r="A260" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B260" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="C260" s="2">
-        <v>46583</v>
+        <v>46631</v>
       </c>
       <c r="D260" s="2">
-        <v>46589</v>
+        <v>46660</v>
       </c>
       <c r="E260" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="F260" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
     </row>
     <row r="261" spans="1:6">
       <c r="A261" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B261" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="C261" s="2">
-        <v>46583</v>
+        <v>46631</v>
       </c>
       <c r="D261" s="2">
-        <v>46589</v>
+        <v>46660</v>
       </c>
       <c r="E261" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="F261" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
     </row>
     <row r="262" spans="1:6">
@@ -6607,79 +6704,79 @@
         <v>12</v>
       </c>
       <c r="B262" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C262" s="2">
-        <v>46600</v>
+        <v>46638</v>
       </c>
       <c r="D262" s="2">
-        <v>46606</v>
+        <v>46644</v>
       </c>
       <c r="E262" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="F262" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="263" spans="1:6">
       <c r="A263" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B263" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C263" s="2">
-        <v>46600</v>
+        <v>46638</v>
       </c>
       <c r="D263" s="2">
-        <v>46630</v>
+        <v>46644</v>
       </c>
       <c r="E263" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="F263" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="264" spans="1:6">
       <c r="A264" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B264" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C264" s="2">
-        <v>46600</v>
+        <v>46652</v>
       </c>
       <c r="D264" s="2">
-        <v>46630</v>
+        <v>46660</v>
       </c>
       <c r="E264" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="F264" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="265" spans="1:6">
       <c r="A265" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B265" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C265" s="2">
-        <v>46600</v>
+        <v>46661</v>
       </c>
       <c r="D265" s="2">
-        <v>46630</v>
+        <v>46667</v>
       </c>
       <c r="E265" t="s">
-        <v>254</v>
+        <v>232</v>
       </c>
       <c r="F265" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="266" spans="1:6">
@@ -6687,19 +6784,19 @@
         <v>13</v>
       </c>
       <c r="B266" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C266" s="2">
-        <v>46600</v>
+        <v>46661</v>
       </c>
       <c r="D266" s="2">
-        <v>46630</v>
+        <v>46691</v>
       </c>
       <c r="E266" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="F266" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="267" spans="1:6">
@@ -6707,19 +6804,19 @@
         <v>13</v>
       </c>
       <c r="B267" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C267" s="2">
-        <v>46600</v>
+        <v>46661</v>
       </c>
       <c r="D267" s="2">
-        <v>46630</v>
+        <v>46691</v>
       </c>
       <c r="E267" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="F267" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="268" spans="1:6">
@@ -6727,19 +6824,19 @@
         <v>13</v>
       </c>
       <c r="B268" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C268" s="2">
-        <v>46600</v>
+        <v>46661</v>
       </c>
       <c r="D268" s="2">
-        <v>46630</v>
+        <v>46691</v>
       </c>
       <c r="E268" t="s">
-        <v>257</v>
+        <v>194</v>
       </c>
       <c r="F268" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="269" spans="1:6">
@@ -6747,19 +6844,19 @@
         <v>13</v>
       </c>
       <c r="B269" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C269" s="2">
-        <v>46600</v>
+        <v>46661</v>
       </c>
       <c r="D269" s="2">
-        <v>46630</v>
+        <v>46691</v>
       </c>
       <c r="E269" t="s">
-        <v>236</v>
+        <v>184</v>
       </c>
       <c r="F269" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="270" spans="1:6">
@@ -6767,19 +6864,19 @@
         <v>13</v>
       </c>
       <c r="B270" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C270" s="2">
-        <v>46600</v>
+        <v>46661</v>
       </c>
       <c r="D270" s="2">
-        <v>46630</v>
+        <v>46691</v>
       </c>
       <c r="E270" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="F270" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="271" spans="1:6">
@@ -6787,19 +6884,19 @@
         <v>13</v>
       </c>
       <c r="B271" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C271" s="2">
-        <v>46600</v>
+        <v>46661</v>
       </c>
       <c r="D271" s="2">
-        <v>46630</v>
+        <v>46691</v>
       </c>
       <c r="E271" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="F271" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="272" spans="1:6">
@@ -6807,59 +6904,59 @@
         <v>12</v>
       </c>
       <c r="B272" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C272" s="2">
-        <v>46607</v>
+        <v>46675</v>
       </c>
       <c r="D272" s="2">
-        <v>46613</v>
+        <v>46681</v>
       </c>
       <c r="E272" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="F272" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="273" spans="1:6">
       <c r="A273" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B273" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="C273" s="2">
-        <v>46607</v>
+        <v>46675</v>
       </c>
       <c r="D273" s="2">
-        <v>46613</v>
+        <v>46681</v>
       </c>
       <c r="E273" t="s">
-        <v>260</v>
+        <v>244</v>
       </c>
       <c r="F273" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="274" spans="1:6">
       <c r="A274" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B274" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C274" s="2">
-        <v>46631</v>
+        <v>46692</v>
       </c>
       <c r="D274" s="2">
-        <v>46637</v>
+        <v>46721</v>
       </c>
       <c r="E274" t="s">
-        <v>261</v>
+        <v>194</v>
       </c>
       <c r="F274" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
     </row>
     <row r="275" spans="1:6">
@@ -6867,19 +6964,19 @@
         <v>13</v>
       </c>
       <c r="B275" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C275" s="2">
-        <v>46631</v>
+        <v>46692</v>
       </c>
       <c r="D275" s="2">
-        <v>46660</v>
+        <v>46721</v>
       </c>
       <c r="E275" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="F275" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="276" spans="1:6">
@@ -6887,19 +6984,19 @@
         <v>13</v>
       </c>
       <c r="B276" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C276" s="2">
-        <v>46631</v>
+        <v>46692</v>
       </c>
       <c r="D276" s="2">
-        <v>46660</v>
+        <v>46721</v>
       </c>
       <c r="E276" t="s">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="F276" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="277" spans="1:6">
@@ -6907,119 +7004,119 @@
         <v>13</v>
       </c>
       <c r="B277" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C277" s="2">
-        <v>46631</v>
+        <v>46692</v>
       </c>
       <c r="D277" s="2">
-        <v>46660</v>
+        <v>46721</v>
       </c>
       <c r="E277" t="s">
-        <v>263</v>
+        <v>240</v>
       </c>
       <c r="F277" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="278" spans="1:6">
       <c r="A278" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B278" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C278" s="2">
-        <v>46631</v>
+        <v>46699</v>
       </c>
       <c r="D278" s="2">
-        <v>46660</v>
+        <v>46705</v>
       </c>
       <c r="E278" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="F278" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="279" spans="1:6">
       <c r="A279" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B279" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C279" s="2">
-        <v>46631</v>
+        <v>46713</v>
       </c>
       <c r="D279" s="2">
-        <v>46660</v>
+        <v>46721</v>
       </c>
       <c r="E279" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="F279" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="280" spans="1:6">
       <c r="A280" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B280" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C280" s="2">
-        <v>46638</v>
+        <v>46722</v>
       </c>
       <c r="D280" s="2">
-        <v>46644</v>
+        <v>46728</v>
       </c>
       <c r="E280" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="F280" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="281" spans="1:6">
       <c r="A281" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B281" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C281" s="2">
-        <v>46652</v>
+        <v>46722</v>
       </c>
       <c r="D281" s="2">
-        <v>46660</v>
+        <v>46752</v>
       </c>
       <c r="E281" t="s">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="F281" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
     </row>
     <row r="282" spans="1:6">
       <c r="A282" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B282" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C282" s="2">
-        <v>46661</v>
+        <v>46722</v>
       </c>
       <c r="D282" s="2">
-        <v>46667</v>
+        <v>46752</v>
       </c>
       <c r="E282" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="F282" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
     </row>
     <row r="283" spans="1:6">
@@ -7027,19 +7124,19 @@
         <v>13</v>
       </c>
       <c r="B283" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C283" s="2">
-        <v>46661</v>
+        <v>46722</v>
       </c>
       <c r="D283" s="2">
-        <v>46691</v>
+        <v>46752</v>
       </c>
       <c r="E283" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="F283" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="284" spans="1:6">
@@ -7047,19 +7144,19 @@
         <v>13</v>
       </c>
       <c r="B284" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C284" s="2">
-        <v>46661</v>
+        <v>46722</v>
       </c>
       <c r="D284" s="2">
-        <v>46691</v>
+        <v>46752</v>
       </c>
       <c r="E284" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="F284" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="285" spans="1:6">
@@ -7067,19 +7164,19 @@
         <v>13</v>
       </c>
       <c r="B285" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C285" s="2">
-        <v>46661</v>
+        <v>46722</v>
       </c>
       <c r="D285" s="2">
-        <v>46691</v>
+        <v>46752</v>
       </c>
       <c r="E285" t="s">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="F285" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="286" spans="1:6">
@@ -7087,19 +7184,19 @@
         <v>13</v>
       </c>
       <c r="B286" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C286" s="2">
-        <v>46661</v>
+        <v>46722</v>
       </c>
       <c r="D286" s="2">
-        <v>46691</v>
+        <v>46752</v>
       </c>
       <c r="E286" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="F286" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="287" spans="1:6">
@@ -7110,16 +7207,16 @@
         <v>37</v>
       </c>
       <c r="C287" s="2">
-        <v>46661</v>
+        <v>46722</v>
       </c>
       <c r="D287" s="2">
-        <v>46691</v>
+        <v>46752</v>
       </c>
       <c r="E287" t="s">
-        <v>272</v>
+        <v>259</v>
       </c>
       <c r="F287" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="288" spans="1:6">
@@ -7127,19 +7224,19 @@
         <v>13</v>
       </c>
       <c r="B288" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C288" s="2">
-        <v>46661</v>
+        <v>46722</v>
       </c>
       <c r="D288" s="2">
-        <v>46691</v>
+        <v>46752</v>
       </c>
       <c r="E288" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="F288" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="289" spans="1:6">
@@ -7147,19 +7244,19 @@
         <v>13</v>
       </c>
       <c r="B289" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C289" s="2">
-        <v>46661</v>
+        <v>46722</v>
       </c>
       <c r="D289" s="2">
-        <v>46691</v>
+        <v>46752</v>
       </c>
       <c r="E289" t="s">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="F289" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="290" spans="1:6">
@@ -7167,79 +7264,79 @@
         <v>13</v>
       </c>
       <c r="B290" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C290" s="2">
-        <v>46661</v>
+        <v>46722</v>
       </c>
       <c r="D290" s="2">
-        <v>46691</v>
+        <v>46752</v>
       </c>
       <c r="E290" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="F290" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="291" spans="1:6">
       <c r="A291" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B291" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C291" s="2">
-        <v>46675</v>
+        <v>46722</v>
       </c>
       <c r="D291" s="2">
-        <v>46681</v>
+        <v>46752</v>
       </c>
       <c r="E291" t="s">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="F291" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
     </row>
     <row r="292" spans="1:6">
       <c r="A292" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B292" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C292" s="2">
-        <v>46675</v>
+        <v>46722</v>
       </c>
       <c r="D292" s="2">
-        <v>46681</v>
+        <v>46752</v>
       </c>
       <c r="E292" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="F292" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
     </row>
     <row r="293" spans="1:6">
       <c r="A293" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B293" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C293" s="2">
-        <v>46692</v>
+        <v>46722</v>
       </c>
       <c r="D293" s="2">
-        <v>46698</v>
+        <v>46752</v>
       </c>
       <c r="E293" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="F293" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
     </row>
     <row r="294" spans="1:6">
@@ -7247,19 +7344,19 @@
         <v>13</v>
       </c>
       <c r="B294" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C294" s="2">
-        <v>46692</v>
+        <v>46722</v>
       </c>
       <c r="D294" s="2">
-        <v>46721</v>
+        <v>46752</v>
       </c>
       <c r="E294" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="F294" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="295" spans="1:6">
@@ -7267,19 +7364,19 @@
         <v>13</v>
       </c>
       <c r="B295" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C295" s="2">
-        <v>46692</v>
+        <v>46722</v>
       </c>
       <c r="D295" s="2">
-        <v>46721</v>
+        <v>46752</v>
       </c>
       <c r="E295" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="F295" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="296" spans="1:6">
@@ -7287,19 +7384,19 @@
         <v>13</v>
       </c>
       <c r="B296" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C296" s="2">
-        <v>46692</v>
+        <v>46722</v>
       </c>
       <c r="D296" s="2">
-        <v>46721</v>
+        <v>46752</v>
       </c>
       <c r="E296" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="F296" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="297" spans="1:6">
@@ -7307,19 +7404,19 @@
         <v>13</v>
       </c>
       <c r="B297" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C297" s="2">
-        <v>46692</v>
+        <v>46722</v>
       </c>
       <c r="D297" s="2">
-        <v>46721</v>
+        <v>46752</v>
       </c>
       <c r="E297" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="F297" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="298" spans="1:6">
@@ -7327,39 +7424,39 @@
         <v>13</v>
       </c>
       <c r="B298" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C298" s="2">
-        <v>46692</v>
+        <v>46722</v>
       </c>
       <c r="D298" s="2">
-        <v>46721</v>
+        <v>46752</v>
       </c>
       <c r="E298" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="F298" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="299" spans="1:6">
       <c r="A299" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B299" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C299" s="2">
-        <v>46713</v>
+        <v>46722</v>
       </c>
       <c r="D299" s="2">
-        <v>46721</v>
+        <v>46752</v>
       </c>
       <c r="E299" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="F299" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
     </row>
     <row r="300" spans="1:6">
@@ -7367,7 +7464,7 @@
         <v>13</v>
       </c>
       <c r="B300" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C300" s="2">
         <v>46722</v>
@@ -7376,10 +7473,10 @@
         <v>46752</v>
       </c>
       <c r="E300" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="F300" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="301" spans="1:6">
@@ -7387,7 +7484,7 @@
         <v>13</v>
       </c>
       <c r="B301" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C301" s="2">
         <v>46722</v>
@@ -7396,10 +7493,10 @@
         <v>46752</v>
       </c>
       <c r="E301" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="F301" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="302" spans="1:6">
@@ -7407,7 +7504,7 @@
         <v>13</v>
       </c>
       <c r="B302" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C302" s="2">
         <v>46722</v>
@@ -7416,10 +7513,10 @@
         <v>46752</v>
       </c>
       <c r="E302" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="F302" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="303" spans="1:6">
@@ -7427,7 +7524,7 @@
         <v>13</v>
       </c>
       <c r="B303" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C303" s="2">
         <v>46722</v>
@@ -7436,10 +7533,10 @@
         <v>46752</v>
       </c>
       <c r="E303" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="F303" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="304" spans="1:6">
@@ -7447,7 +7544,7 @@
         <v>13</v>
       </c>
       <c r="B304" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C304" s="2">
         <v>46722</v>
@@ -7456,10 +7553,10 @@
         <v>46752</v>
       </c>
       <c r="E304" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="F304" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="305" spans="1:6">
@@ -7467,7 +7564,7 @@
         <v>13</v>
       </c>
       <c r="B305" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C305" s="2">
         <v>46722</v>
@@ -7476,10 +7573,10 @@
         <v>46752</v>
       </c>
       <c r="E305" t="s">
-        <v>287</v>
+        <v>10</v>
       </c>
       <c r="F305" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="306" spans="1:6">
@@ -7487,7 +7584,7 @@
         <v>13</v>
       </c>
       <c r="B306" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C306" s="2">
         <v>46722</v>
@@ -7496,10 +7593,10 @@
         <v>46752</v>
       </c>
       <c r="E306" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="F306" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="307" spans="1:6">
@@ -7507,7 +7604,7 @@
         <v>13</v>
       </c>
       <c r="B307" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C307" s="2">
         <v>46722</v>
@@ -7516,10 +7613,10 @@
         <v>46752</v>
       </c>
       <c r="E307" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="F307" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="308" spans="1:6">
@@ -7527,7 +7624,7 @@
         <v>13</v>
       </c>
       <c r="B308" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C308" s="2">
         <v>46722</v>
@@ -7536,10 +7633,10 @@
         <v>46752</v>
       </c>
       <c r="E308" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="F308" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="309" spans="1:6">
@@ -7547,7 +7644,7 @@
         <v>13</v>
       </c>
       <c r="B309" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C309" s="2">
         <v>46722</v>
@@ -7556,50 +7653,770 @@
         <v>46752</v>
       </c>
       <c r="E309" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="F309" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="310" spans="1:6">
       <c r="A310" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B310" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C310" s="2">
-        <v>46729</v>
+        <v>46722</v>
       </c>
       <c r="D310" s="2">
-        <v>46735</v>
+        <v>46752</v>
       </c>
       <c r="E310" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="F310" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
     </row>
     <row r="311" spans="1:6">
       <c r="A311" t="s">
+        <v>13</v>
+      </c>
+      <c r="B311" t="s">
+        <v>39</v>
+      </c>
+      <c r="C311" s="2">
+        <v>46722</v>
+      </c>
+      <c r="D311" s="2">
+        <v>46752</v>
+      </c>
+      <c r="E311" t="s">
+        <v>282</v>
+      </c>
+      <c r="F311" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6">
+      <c r="A312" t="s">
+        <v>13</v>
+      </c>
+      <c r="B312" t="s">
+        <v>39</v>
+      </c>
+      <c r="C312" s="2">
+        <v>46722</v>
+      </c>
+      <c r="D312" s="2">
+        <v>46752</v>
+      </c>
+      <c r="E312" t="s">
+        <v>283</v>
+      </c>
+      <c r="F312" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6">
+      <c r="A313" t="s">
+        <v>13</v>
+      </c>
+      <c r="B313" t="s">
+        <v>39</v>
+      </c>
+      <c r="C313" s="2">
+        <v>46722</v>
+      </c>
+      <c r="D313" s="2">
+        <v>46752</v>
+      </c>
+      <c r="E313" t="s">
+        <v>284</v>
+      </c>
+      <c r="F313" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6">
+      <c r="A314" t="s">
+        <v>13</v>
+      </c>
+      <c r="B314" t="s">
+        <v>32</v>
+      </c>
+      <c r="C314" s="2">
+        <v>46722</v>
+      </c>
+      <c r="D314" s="2">
+        <v>46752</v>
+      </c>
+      <c r="E314" t="s">
+        <v>285</v>
+      </c>
+      <c r="F314" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6">
+      <c r="A315" t="s">
+        <v>13</v>
+      </c>
+      <c r="B315" t="s">
+        <v>32</v>
+      </c>
+      <c r="C315" s="2">
+        <v>46722</v>
+      </c>
+      <c r="D315" s="2">
+        <v>46752</v>
+      </c>
+      <c r="E315" t="s">
+        <v>286</v>
+      </c>
+      <c r="F315" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6">
+      <c r="A316" t="s">
+        <v>13</v>
+      </c>
+      <c r="B316" t="s">
+        <v>32</v>
+      </c>
+      <c r="C316" s="2">
+        <v>46722</v>
+      </c>
+      <c r="D316" s="2">
+        <v>46752</v>
+      </c>
+      <c r="E316" t="s">
+        <v>287</v>
+      </c>
+      <c r="F316" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="317" spans="1:6">
+      <c r="A317" t="s">
+        <v>13</v>
+      </c>
+      <c r="B317" t="s">
+        <v>32</v>
+      </c>
+      <c r="C317" s="2">
+        <v>46722</v>
+      </c>
+      <c r="D317" s="2">
+        <v>46752</v>
+      </c>
+      <c r="E317" t="s">
+        <v>288</v>
+      </c>
+      <c r="F317" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="318" spans="1:6">
+      <c r="A318" t="s">
+        <v>13</v>
+      </c>
+      <c r="B318" t="s">
+        <v>34</v>
+      </c>
+      <c r="C318" s="2">
+        <v>46722</v>
+      </c>
+      <c r="D318" s="2">
+        <v>46752</v>
+      </c>
+      <c r="E318" t="s">
+        <v>289</v>
+      </c>
+      <c r="F318" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="319" spans="1:6">
+      <c r="A319" t="s">
+        <v>13</v>
+      </c>
+      <c r="B319" t="s">
+        <v>34</v>
+      </c>
+      <c r="C319" s="2">
+        <v>46722</v>
+      </c>
+      <c r="D319" s="2">
+        <v>46752</v>
+      </c>
+      <c r="E319" t="s">
+        <v>290</v>
+      </c>
+      <c r="F319" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="320" spans="1:6">
+      <c r="A320" t="s">
+        <v>13</v>
+      </c>
+      <c r="B320" t="s">
+        <v>34</v>
+      </c>
+      <c r="C320" s="2">
+        <v>46722</v>
+      </c>
+      <c r="D320" s="2">
+        <v>46752</v>
+      </c>
+      <c r="E320" t="s">
+        <v>291</v>
+      </c>
+      <c r="F320" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6">
+      <c r="A321" t="s">
+        <v>13</v>
+      </c>
+      <c r="B321" t="s">
+        <v>34</v>
+      </c>
+      <c r="C321" s="2">
+        <v>46722</v>
+      </c>
+      <c r="D321" s="2">
+        <v>46752</v>
+      </c>
+      <c r="E321" t="s">
+        <v>292</v>
+      </c>
+      <c r="F321" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="322" spans="1:6">
+      <c r="A322" t="s">
+        <v>13</v>
+      </c>
+      <c r="B322" t="s">
+        <v>34</v>
+      </c>
+      <c r="C322" s="2">
+        <v>46722</v>
+      </c>
+      <c r="D322" s="2">
+        <v>46752</v>
+      </c>
+      <c r="E322" t="s">
+        <v>293</v>
+      </c>
+      <c r="F322" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="323" spans="1:6">
+      <c r="A323" t="s">
+        <v>13</v>
+      </c>
+      <c r="B323" t="s">
+        <v>34</v>
+      </c>
+      <c r="C323" s="2">
+        <v>46722</v>
+      </c>
+      <c r="D323" s="2">
+        <v>46752</v>
+      </c>
+      <c r="E323" t="s">
+        <v>294</v>
+      </c>
+      <c r="F323" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6">
+      <c r="A324" t="s">
+        <v>13</v>
+      </c>
+      <c r="B324" t="s">
+        <v>34</v>
+      </c>
+      <c r="C324" s="2">
+        <v>46722</v>
+      </c>
+      <c r="D324" s="2">
+        <v>46752</v>
+      </c>
+      <c r="E324" t="s">
+        <v>295</v>
+      </c>
+      <c r="F324" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="325" spans="1:6">
+      <c r="A325" t="s">
+        <v>13</v>
+      </c>
+      <c r="B325" t="s">
+        <v>34</v>
+      </c>
+      <c r="C325" s="2">
+        <v>46722</v>
+      </c>
+      <c r="D325" s="2">
+        <v>46752</v>
+      </c>
+      <c r="E325" t="s">
+        <v>296</v>
+      </c>
+      <c r="F325" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="326" spans="1:6">
+      <c r="A326" t="s">
+        <v>13</v>
+      </c>
+      <c r="B326" t="s">
+        <v>34</v>
+      </c>
+      <c r="C326" s="2">
+        <v>46722</v>
+      </c>
+      <c r="D326" s="2">
+        <v>46752</v>
+      </c>
+      <c r="E326" t="s">
+        <v>213</v>
+      </c>
+      <c r="F326" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="327" spans="1:6">
+      <c r="A327" t="s">
+        <v>13</v>
+      </c>
+      <c r="B327" t="s">
+        <v>34</v>
+      </c>
+      <c r="C327" s="2">
+        <v>46722</v>
+      </c>
+      <c r="D327" s="2">
+        <v>46752</v>
+      </c>
+      <c r="E327" t="s">
+        <v>297</v>
+      </c>
+      <c r="F327" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="328" spans="1:6">
+      <c r="A328" t="s">
+        <v>13</v>
+      </c>
+      <c r="B328" t="s">
+        <v>34</v>
+      </c>
+      <c r="C328" s="2">
+        <v>46722</v>
+      </c>
+      <c r="D328" s="2">
+        <v>46752</v>
+      </c>
+      <c r="E328" t="s">
+        <v>298</v>
+      </c>
+      <c r="F328" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="329" spans="1:6">
+      <c r="A329" t="s">
+        <v>13</v>
+      </c>
+      <c r="B329" t="s">
+        <v>35</v>
+      </c>
+      <c r="C329" s="2">
+        <v>46722</v>
+      </c>
+      <c r="D329" s="2">
+        <v>46752</v>
+      </c>
+      <c r="E329" t="s">
+        <v>178</v>
+      </c>
+      <c r="F329" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="330" spans="1:6">
+      <c r="A330" t="s">
+        <v>13</v>
+      </c>
+      <c r="B330" t="s">
+        <v>35</v>
+      </c>
+      <c r="C330" s="2">
+        <v>46722</v>
+      </c>
+      <c r="D330" s="2">
+        <v>46752</v>
+      </c>
+      <c r="E330" t="s">
+        <v>299</v>
+      </c>
+      <c r="F330" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="331" spans="1:6">
+      <c r="A331" t="s">
+        <v>13</v>
+      </c>
+      <c r="B331" t="s">
+        <v>35</v>
+      </c>
+      <c r="C331" s="2">
+        <v>46722</v>
+      </c>
+      <c r="D331" s="2">
+        <v>46752</v>
+      </c>
+      <c r="E331" t="s">
+        <v>300</v>
+      </c>
+      <c r="F331" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="332" spans="1:6">
+      <c r="A332" t="s">
+        <v>13</v>
+      </c>
+      <c r="B332" t="s">
+        <v>35</v>
+      </c>
+      <c r="C332" s="2">
+        <v>46722</v>
+      </c>
+      <c r="D332" s="2">
+        <v>46752</v>
+      </c>
+      <c r="E332" t="s">
+        <v>295</v>
+      </c>
+      <c r="F332" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="333" spans="1:6">
+      <c r="A333" t="s">
+        <v>13</v>
+      </c>
+      <c r="B333" t="s">
+        <v>35</v>
+      </c>
+      <c r="C333" s="2">
+        <v>46722</v>
+      </c>
+      <c r="D333" s="2">
+        <v>46752</v>
+      </c>
+      <c r="E333" t="s">
+        <v>296</v>
+      </c>
+      <c r="F333" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="334" spans="1:6">
+      <c r="A334" t="s">
+        <v>13</v>
+      </c>
+      <c r="B334" t="s">
+        <v>35</v>
+      </c>
+      <c r="C334" s="2">
+        <v>46722</v>
+      </c>
+      <c r="D334" s="2">
+        <v>46752</v>
+      </c>
+      <c r="E334" t="s">
+        <v>301</v>
+      </c>
+      <c r="F334" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="335" spans="1:6">
+      <c r="A335" t="s">
+        <v>13</v>
+      </c>
+      <c r="B335" t="s">
+        <v>41</v>
+      </c>
+      <c r="C335" s="2">
+        <v>46722</v>
+      </c>
+      <c r="D335" s="2">
+        <v>46752</v>
+      </c>
+      <c r="E335" t="s">
+        <v>240</v>
+      </c>
+      <c r="F335" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="336" spans="1:6">
+      <c r="A336" t="s">
+        <v>13</v>
+      </c>
+      <c r="B336" t="s">
+        <v>41</v>
+      </c>
+      <c r="C336" s="2">
+        <v>46722</v>
+      </c>
+      <c r="D336" s="2">
+        <v>46752</v>
+      </c>
+      <c r="E336" t="s">
+        <v>230</v>
+      </c>
+      <c r="F336" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="337" spans="1:6">
+      <c r="A337" t="s">
+        <v>13</v>
+      </c>
+      <c r="B337" t="s">
+        <v>41</v>
+      </c>
+      <c r="C337" s="2">
+        <v>46722</v>
+      </c>
+      <c r="D337" s="2">
+        <v>46752</v>
+      </c>
+      <c r="E337" t="s">
+        <v>302</v>
+      </c>
+      <c r="F337" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="338" spans="1:6">
+      <c r="A338" t="s">
+        <v>13</v>
+      </c>
+      <c r="B338" t="s">
+        <v>41</v>
+      </c>
+      <c r="C338" s="2">
+        <v>46722</v>
+      </c>
+      <c r="D338" s="2">
+        <v>46752</v>
+      </c>
+      <c r="E338" t="s">
+        <v>303</v>
+      </c>
+      <c r="F338" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="339" spans="1:6">
+      <c r="A339" t="s">
+        <v>13</v>
+      </c>
+      <c r="B339" t="s">
+        <v>41</v>
+      </c>
+      <c r="C339" s="2">
+        <v>46722</v>
+      </c>
+      <c r="D339" s="2">
+        <v>46752</v>
+      </c>
+      <c r="E339" t="s">
+        <v>304</v>
+      </c>
+      <c r="F339" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="340" spans="1:6">
+      <c r="A340" t="s">
+        <v>13</v>
+      </c>
+      <c r="B340" t="s">
+        <v>41</v>
+      </c>
+      <c r="C340" s="2">
+        <v>46722</v>
+      </c>
+      <c r="D340" s="2">
+        <v>46752</v>
+      </c>
+      <c r="E340" t="s">
+        <v>305</v>
+      </c>
+      <c r="F340" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="341" spans="1:6">
+      <c r="A341" t="s">
+        <v>13</v>
+      </c>
+      <c r="B341" t="s">
+        <v>41</v>
+      </c>
+      <c r="C341" s="2">
+        <v>46722</v>
+      </c>
+      <c r="D341" s="2">
+        <v>46752</v>
+      </c>
+      <c r="E341" t="s">
+        <v>306</v>
+      </c>
+      <c r="F341" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="342" spans="1:6">
+      <c r="A342" t="s">
+        <v>13</v>
+      </c>
+      <c r="B342" t="s">
+        <v>41</v>
+      </c>
+      <c r="C342" s="2">
+        <v>46722</v>
+      </c>
+      <c r="D342" s="2">
+        <v>46752</v>
+      </c>
+      <c r="E342" t="s">
+        <v>307</v>
+      </c>
+      <c r="F342" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="343" spans="1:6">
+      <c r="A343" t="s">
+        <v>13</v>
+      </c>
+      <c r="B343" t="s">
+        <v>41</v>
+      </c>
+      <c r="C343" s="2">
+        <v>46722</v>
+      </c>
+      <c r="D343" s="2">
+        <v>46752</v>
+      </c>
+      <c r="E343" t="s">
+        <v>308</v>
+      </c>
+      <c r="F343" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="344" spans="1:6">
+      <c r="A344" t="s">
+        <v>13</v>
+      </c>
+      <c r="B344" t="s">
+        <v>41</v>
+      </c>
+      <c r="C344" s="2">
+        <v>46722</v>
+      </c>
+      <c r="D344" s="2">
+        <v>46752</v>
+      </c>
+      <c r="E344" t="s">
+        <v>309</v>
+      </c>
+      <c r="F344" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="345" spans="1:6">
+      <c r="A345" t="s">
+        <v>13</v>
+      </c>
+      <c r="B345" t="s">
+        <v>41</v>
+      </c>
+      <c r="C345" s="2">
+        <v>46722</v>
+      </c>
+      <c r="D345" s="2">
+        <v>46752</v>
+      </c>
+      <c r="E345" t="s">
+        <v>310</v>
+      </c>
+      <c r="F345" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="346" spans="1:6">
+      <c r="A346" t="s">
+        <v>13</v>
+      </c>
+      <c r="B346" t="s">
+        <v>41</v>
+      </c>
+      <c r="C346" s="2">
+        <v>46722</v>
+      </c>
+      <c r="D346" s="2">
+        <v>46752</v>
+      </c>
+      <c r="E346" t="s">
+        <v>311</v>
+      </c>
+      <c r="F346" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="347" spans="1:6">
+      <c r="A347" t="s">
         <v>14</v>
       </c>
-      <c r="B311" t="s">
-        <v>41</v>
-      </c>
-      <c r="C311" s="2">
+      <c r="B347" t="s">
+        <v>40</v>
+      </c>
+      <c r="C347" s="2">
         <v>46729</v>
       </c>
-      <c r="D311" s="2">
+      <c r="D347" s="2">
         <v>46735</v>
       </c>
-      <c r="E311" t="s">
-        <v>293</v>
-      </c>
-      <c r="F311" t="s">
-        <v>296</v>
+      <c r="E347" t="s">
+        <v>312</v>
+      </c>
+      <c r="F347" t="s">
+        <v>315</v>
       </c>
     </row>
   </sheetData>
